--- a/results/evaluation/answers/eval_rag_combined.xlsx
+++ b/results/evaluation/answers/eval_rag_combined.xlsx
@@ -435,17 +435,17 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>a_hu</t>
+          <t>a_hu_top5</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>a_qwen2.5</t>
+          <t>a_qwen2.5_top5</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>a_llama3.1</t>
+          <t>a_llama3.1_top5</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3463,10 +3463,15 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>top_k</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>EM</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -3479,9 +3484,12 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.62</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.6836666666666666</v>
       </c>
     </row>
@@ -3492,9 +3500,12 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.54</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>0.6033333333333334</v>
       </c>
     </row>
@@ -3505,9 +3516,12 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.52</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>0.5875714285714285</v>
       </c>
     </row>

--- a/results/evaluation/answers/eval_rag_combined.xlsx
+++ b/results/evaluation/answers/eval_rag_combined.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,17 +435,62 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>a_hu_top1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>a_hu_top3</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>a_hu_top5</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>a_hu_top10</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>a_qwen2.5_top1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>a_qwen2.5_top3</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>a_qwen2.5_top5</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>a_qwen2.5_top10</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>a_llama3.1_top1</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>a_llama3.1_top3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>a_llama3.1_top5</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>a_llama3.1_top10</t>
         </is>
       </c>
     </row>
@@ -470,12 +515,75 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Amoxicillin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Amoxicillin</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Amoxicillin</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>amoxicillin</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>amoxicillin</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>amoxicillin</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Based on the provided information, here's a summary of the key points related to Lyme disease, its prevention, and treatment:
+### Prevention
+- **Tick Removal**: Prompt removal of attached ticks is crucial to reduce the risk of Lyme disease. The risk of infection increases with the duration of tick attachment. In North America, the risk is small if the tick is removed within 36 hours. CDC recommends using fine-tipped tweezers to grasp the tick firmly and pull it straight out without twisting or crushing it. After removal, clean the wound and hands with alcohol or soap and water. The tick should be disposed of properly, and the bitten person should record the location and date of the bite for future reference.
+- **Preventive Antibiotics**: If a deer tick is found attached for 36 hours or more, a single dose of doxycycline may be administered within 72 hours to reduce the risk of Lyme disease. However, this is not generally recommended for all tick bites due to the low risk of infection.
+### Early Localized Infection
+- **Erythema Migrans (EM) Rash**: Approximately 80% of Lyme infections start with a rash at the site of a tick bite. The rash usually appears 1-2 weeks after the bite and expands, reaching a diameter of 5-70 cm. It is often circular or oval, red or bluish, and may form a "bull's eye" pattern in about 79% of cases in Europe but only 19% in the U.S. The rash may feel warm and takes up to four weeks to resolve if untreated.
+- **Symptoms**: The rash is often accompanied by flu-like symptoms such as fatigue, headache, body aches, fever, and chills. These symptoms may also appear without a rash and can persist after the rash has disappeared.
+### Treatment
+- **Doxycycline**: Doxycycline is a broad-spectrum antibiotic used to treat Lyme disease. It is effective when administered promptly after a tick bite. It is also used for other infections caused by bacteria and certain parasites.
+- **Amoxicillin**: Amoxicillin is another antibiotic used to treat early cutaneous Lyme borreliosis. It is effective and safe, but its effectiveness and safety are neither better nor worse than other commonly used antibiotics for Lyme disease.
+### Additional Considerations
+- **Coinfections**: People with Lyme disease should be investigated for possible coinfections with other tick-borne diseases such as ehrlichiosis and babesiosis, especially if they have high fever for more than two days or if their symptoms do not improve despite antibiotic treatment.
+- **Asymptomatic Infection**: Asymptomatic infection can occur, but it is less common in the U.S. compared to Europe.
+This summary provides a comprehensive overview of the prevention, early signs, and treatment options for Lyme disease, emphasizing the importance of prompt action and proper medical guidance.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Amoxicillin</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Amoxicillin</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Azithromycin</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>The provided text does not contain a specific question that can be answered with a single final answer. However, I can provide a summary of the information related to Lyme disease and its treatment.
+Lyme disease is a bacterial infection caused by Borrelia burgdorferi, which is transmitted to humans through the bite of an infected tick. The disease can cause a range of symptoms, including a distinctive rash called erythema migrans, fever, headache, body aches, and fatigue.
+The text mentions that in Europe, 41% of people treated for facial palsy had other lingering symptoms at follow-up up to 6 months later, including 28% with numbness or altered sensation and 14% with fatigue or concentration problems.
+It also mentions that tick removal is crucial in preventing Lyme disease, and that a single dose of doxycycline administered within 72 hours after removal may reduce the risk of Lyme disease.
+The text also discusses the use of doxycycline and amoxicillin in the treatment of Lyme disease, as well as their use in other medical conditions.
+If you have a specific question related to Lyme disease or its treatment, I can try to provide a more detailed answer.</t>
         </is>
       </c>
     </row>
@@ -500,10 +608,56 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Based on the provided text, the recommended treatment for Lyme disease is **doxycycline**.
+The text explicitly states: "The recommended treatment for Lyme disease is doxycycline." It further notes that doxycycline is the first choice for early localized disease and is available as an alternative for neurologic complications. While ceftriaxone is preferred for retreatment in cases of failure, doxycycline remains the primary recommended agent.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>doxycycline</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ceftriaxone</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>doxycycline</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>doxycycline</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Ceftriaxone</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Doxycycline</t>
         </is>
@@ -538,6 +692,51 @@
           <t>Propylthiouracil</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PTU</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PTU</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -560,12 +759,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Azithromycin</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Erythromycin or amoxicillin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Azithromycin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>erythromycin</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>erythromycin</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>erythromycin</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Based on the provided information, Doxycycline is a broad-spectrum antibiotic that is effective against a variety of bacterial and parasitic infections, including Chlamydia trachomatis, which causes trachoma and reactive arthritis. It is also used to treat Lyme disease, syphilis, and other conditions. Here's a summary of its use in treating conditions related to Chlamydia trachomatis and other infections:
+### Chlamydia Trachomatis and Trachoma
+- **Trachoma:** Doxycycline is used to treat trachoma, a disease caused by Chlamydia trachomatis. It is part of the SAFE strategy (Surgery, Antibiotics, Facial cleanliness, and Environmental improvements) to control and eliminate trachoma.
+- **Reactive Arthritis:** Doxycycline can be used to treat reactive arthritis, which is often associated with Chlamydia trachomatis infections. This condition typically affects young men and can cause arthritis, conjunctivitis, and urethral inflammation.
+### Chlamydia in Infants
+- **Neonatal Infections:** Doxycycline is used to treat chlamydia infections in newborns, which can cause conjunctivitis, pneumonia, and other complications. Infants born to mothers with chlamydia have a high risk of developing these infections.
+### Syphilis
+- **Syphilis:** Doxycycline is an alternative treatment for syphilis, particularly in cases where penicillin is contraindicated. It is not the first-line treatment but can be used in specific scenarios.
+### Lyme Disease
+- **Lyme Disease:** Doxycycline is the first-line oral antibiotic for early localized Lyme disease. It is effective against Borrelia bacteria and is recommended for individuals who are not pregnant, breastfeeding, or under eight years of age. For early disseminated or late-stage Lyme disease, intravenous ceftriaxone is preferred, but doxycycline can be used as an alternative.
+### Other Conditions
+- **Other Bacterial and Parasitic Infections:** Doxycycline is also used to treat other bacterial and parasitic infections, such as malaria, cholera, and typhus.
+### Side Effects and Precautions
+- **Side Effects:** Common side effects include diarrhea, nausea, vomiting, abdominal pain, and increased risk of sunburn.
+- **Contraindications:** Doxycycline is contraindicated in children under eight years of age, pregnant women, and breastfeeding women. It should be used with caution in individuals with a history of gastrointestinal disorders or photosensitivity.
+### Summary
+Doxycycline is a versatile antibiotic that plays a crucial role in treating infections caused by Chlamydia trachomatis, including trachoma, reactive arthritis, and neonatal infections. It is also effective against other bacterial and parasitic infections, such as syphilis and Lyme disease. However, it should be used with caution in certain populations and under medical supervision.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Erythromycin</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Erythromycin</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Erythromycin</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Based on the provided text, the answer to the question "What is the recommended treatment for chlamydia infection?" is:
+Doxycycline is a recommended treatment for chlamydia infection.
+This is mentioned in the text about Doxycycline, which states that it is used to treat bacterial infections, including chlamydia infections.
+Additionally, the text about Chlamydia infection mentions that doxycycline is used to treat chlamydia eye infection in newborns, and that it is also used to treat reactive arthritis caused by chlamydia infection.
+Therefore, the recommended treatment for chlamydia infection is doxycycline.</t>
         </is>
       </c>
     </row>
@@ -585,17 +849,62 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Echinocandin</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Echinocandin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>echinocandin</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>echinocandin</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>echinocandin</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Anidulafungin</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Echinocandin</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Echinocandin</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Caspofungin</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Anidulafungin</t>
         </is>
       </c>
     </row>
@@ -615,15 +924,60 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Macrolides or clindamycin</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Macrolides</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Erythromycin</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Azithromycin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>erythromycin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cephalexin</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Cephalexin</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>erythromycin</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Erythromycin</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Erythromycin</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Erythromycin</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Erythromycin</t>
         </is>
@@ -658,6 +1012,51 @@
           <t>Bupropion</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Bupropion is the antidepressant that should not be prescribed to individuals with bulimia nervosa.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Bupropion.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -680,10 +1079,55 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>propranolol</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>propranolol</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>propranolol</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Propranolol</t>
         </is>
@@ -705,15 +1149,60 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Oxcarbazepine</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Oxcarbazepine</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Oxcarbazepine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>oxcarbazepine</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>oxcarbazepine</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Oxcarbazepine</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>lamotrigine</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Baclofen</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Lamotrigine</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Lamotrigine</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Lamotrigine</t>
         </is>
@@ -740,12 +1229,63 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Benzodiazepines</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Benzodiazepines</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Benzodiazepines</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>Benzodiazepine</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Benzodiazepines</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Benzodiazepine</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the articles, lorazepam is a benzodiazepine that is commonly used for treating convulsive status epilepticus, alcohol withdrawal syndrome, and other conditions that require anticonvulsant and central nervous system depressant properties. It is noted for its effectiveness in terminating acute seizures and its lower risk of continuing seizures compared to diazepam and intravenous phenytoin. However, lorazepam can induce prolonged sedation, and its use as a long-term prophylactic treatment for resistant absence seizures is limited due to gradual tolerance.
+In the context of generalized anxiety disorder (GAD), benzodiazepines like lorazepam are used to alleviate anxiety symptoms, but their use is controversial due to the risk of dependence and tolerance. While they provide rapid relief, they are not recommended for long-term use. Instead, selective serotonin reuptake inhibitors (SSRIs) and other antidepressants are often considered first-line treatments for GAD, especially in adults, as they have been shown to be safe and effective.
+Regarding comorbid conditions, benzodiazepines such as lorazepam should be used cautiously in patients with substance use disorders due to their addictive properties. For patients with GAD and ADHD, the comorbidity is significant, with GAD being the most prevalent anxiety disorder in individuals with ADHD. Additionally, GAD is often comorbid with alcohol use disorder and other substance use disorders, which complicates treatment decisions.
+In summary, while lorazepam is effective for acute conditions requiring anticonvulsant and sedative properties, its use in chronic conditions like GAD is limited due to the risks of dependence and tolerance. For GAD, SSRIs and other antidepressants are generally preferred for long-term management.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Benzodiazepine</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Benzodiazepines</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Benzodiazepines</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Lorazepam is a benzodiazepine that is used to treat various conditions, including seizures, status epilepticus, and alcohol withdrawal syndrome. It is also used to calm the acutely agitated individual and can be given via an intramuscular injection. Lorazepam has a lower risk of continuing seizures that might require additional medication compared to diazepam and intravenous phenytoin. It is also effective in the short-term treatment of psychiatric emergencies such as acute psychosis as in schizophrenia or mania, bringing about rapid tranquillization and sedation until the effects of lithium or neuroleptics (antipsychotics) take effect.
+In the context of generalized anxiety disorder (GAD), benzodiazepines like lorazepam are sometimes used as a treatment option, but they are not considered first-line therapies due to the risk of dependence and tolerance. Cognitive behavioral therapy (CBT) is widely regarded as the first-line psychological therapy for treating GAD. Antidepressants, such as selective serotonin reuptake inhibitors (SSRIs), are also commonly used to treat GAD.
+Lorazepam has a number of effects that make it a good option for treating anxiety, including anxiolytic, hypnotic (sleep-inducing), muscle relaxant, anticonvulsant, and amnestic (impair short-term memory) properties. However, benzodiazepines have a risk of dependence and tolerance, and their use should be carefully considered in patients with a history of substance use disorder.
+In terms of comorbidity, patients with GAD often have comorbid conditions such as depression, substance use disorder, and attention deficit hyperactivity disorder (ADHD). The treatment of GAD must be adapted for different comorbidities, and pharmacological approaches must be carefully considered to avoid exacerbating the comorbid condition.</t>
         </is>
       </c>
     </row>
@@ -770,12 +1310,57 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Atovaquone</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Atovaquone</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Atovaquone</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>atovaquone</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>atovaquone</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>atovaquone</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>atovaquone</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Atovaquone</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>Dapsone</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Dapsone</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Atovaquone</t>
         </is>
       </c>
     </row>
@@ -795,17 +1380,73 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Oxazepam</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Lorazepam</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>lorazepam</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>lorazepam</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>lorazepam</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the article, lorazepam is a benzodiazepine that does not require oxidation for its metabolism, making it particularly suitable for individuals with advanced-stage liver disease. This characteristic sets lorazepam apart from other benzodiazepines, which may require hepatic metabolism and could pose risks for those with compromised liver function. Lorazepam's favorable profile in this regard makes it a preferred choice for managing conditions such as anxiety and insomnia in patients with advanced liver disease, where other benzodiazepines might be contraindicated due to the risk of accumulation or toxicity.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>The text discusses the properties, uses, and risks associated with benzodiazepines, a class of central nervous system depressant drugs. Key points include:
+* Benzodiazepines are used to treat conditions such as anxiety disorders, insomnia, and seizures.
+* They work by enhancing the effect of the neurotransmitter gamma-aminobutyric acid (GABA) at the GABA_A receptor.
+* Benzodiazepines are categorized as short, intermediate, and long-acting, with short and intermediate-acting benzodiazepines preferred for treating insomnia and longer-acting benzodiazepines recommended for treating anxiety.
+* Short-term use of benzodiazepines is generally considered safe and effective, but long-term use can cause impaired thinking or memory loss, anxiety, depression, irritability, paranoia, aggression, and other adverse effects.
+* Benzodiazepines are associated with an increased risk of suicide due to aggression, impulsivity, and negative withdrawal effects.
+* The elderly are at an increased risk of both short-term and long-term adverse effects, and as a result, benzodiazepines should be used with caution in this population.
+* Benzodiazepines are often prescribed for as-needed use, which is understudied but is likely safe and effective for intermittent short-term use.
+* Benzodiazepines are considered major habit-forming substances and are often misused, particularly among individuals who engage in polysubstance use.
+* Non-medical benzodiazepine use is associated with a range of health consequences, including dependence, tolerance, and withdrawal symptoms.
+* Benzodiazepines require special precaution if used in the elderly, during pregnancy, in children, alcohol or drug-dependent individuals, and individuals with comorbid psychiatric disorders.
+Overall, the text highlights the potential benefits and risks associated with benzodiazepines and emphasizes the need for careful consideration and caution when prescribing these medications.</t>
         </is>
       </c>
     </row>
@@ -838,6 +1479,65 @@
           <t>Retinoids</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Retinoids</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Retinoids</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Retinoids</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Retinoids</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Based on the provided articles, it is clear that doxycycline is a broad-spectrum antibiotic used to treat various bacterial infections, including syphilis. Given this information, we can infer that doxycycline can be used in the management of syphilis, a condition mentioned in the prompt.
+For the management of syphilis, doxycycline is one of the antibiotics that can be used, particularly in early-stage syphilis. However, the primary treatment for syphilis is penicillin, which is highly effective and recommended by the CDC and WHO. Doxycycline can be an alternative for patients who are allergic to penicillin or in cases where penicillin is not available. It is important to note that doxycycline is not the first-line treatment for syphilis, but it can be used in specific circumstances.
+In the context of acne vulgaris, while doxycycline is used to treat acne, it is not typically the first-line treatment. First-line treatments for acne include topical retinoids, benzoyl peroxide, and topical or oral antibiotics. Doxycycline is often used when other treatments are ineffective or when there is a need for a systemic approach, such as in moderate to severe acne or acne with significant inflammation.
+In summary, doxycycline is an effective antibiotic for treating syphilis when penicillin is not an option, and it can be used in the management of acne, particularly in more severe cases or when other treatments are ineffective. However, it is not the first-line treatment for either condition.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Oral retinoids</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Retinoids</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Retinoids</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Based on the provided articles, here are some key points related to the treatment of acne and the use of antibiotics:
+1. **Treatment of Acne**: Many different treatments exist for acne, including alpha hydroxy acid, anti-androgen medications, antibiotics, antiseborrheic medications, azelaic acid, benzoyl peroxide, hormonal treatments, keratolytic soaps, nicotinamide (niacinamide), retinoids, and salicylic acid.
+2. **Antibiotics for Acne**: Antibiotics, such as doxycycline and azithromycin, are commonly used to treat acne. They work by killing bacteria that cause acne, reducing inflammation, and normalizing skin cell shedding and sebum production.
+3. **Side Effects of Antibiotics**: Common side effects of antibiotics, such as doxycycline and azithromycin, include diarrhea, nausea, vomiting, abdominal pain, and an increased risk of sunburn.
+4. **Use of Antibiotics in Pregnancy**: The use of antibiotics during pregnancy is not recommended, and the safety of azithromycin during pregnancy is not confirmed.
+5. **Retinoids for Acne**: Retinoids, such as isotretinoin, are used to treat severe acne. However, they can have toxic effects, including hypervitaminosis A, anorexia, skin lesions, hair loss, hepatosplenomegaly, papilloedema, bleeding, general malaise, pseudotumor cerebri, and death.
+6. **Long-term Nature of Acne**: Acne is a long-term condition that can persist beyond puberty. Communicating the long-term nature of the condition and providing reliable information about acne can help people know what to expect from treatments.
+In terms of the specific articles, here are some key points:
+* The article on Doxycycline provides information on the use of doxycycline to treat acne, as well as its side effects and potential interactions.
+* The article on Azithromycin provides information on the use of azithromycin to treat acne, as well as its side effects and potential interactions.
+* The article on Retinoids provides information on the use of retinoids to treat acne, as well as their potential toxic effects.
+* The article on Acne Vulgaris provides information on the history of acne, its causes, and its treatment options.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -868,6 +1568,92 @@
           <t>Lithium</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Based on the information provided, here's a summary of the key points regarding the use of various treatments for depression and bipolar disorder:
+1. **Bupropion**:
+   - Effective for treating depression, with evidence supporting its use over placebo.
+   - Can prevent the development of seasonal affective disorder.
+   - Does not typically cause sexual dysfunction or weight gain.
+   - May be effective in treating depression with comorbid anxiety.
+   - Can be used as an adjunct to SSRIs for treatment-resistant depression.
+2. **SSRIs (Selective Serotonin Reuptake Inhibitors)**:
+   - Effective for moderate to severe major depression.
+   - May cause sexual dysfunction and weight gain.
+   - Can be combined with bupropion for treatment-resistant depression.
+   - Not recommended for children and adolescents due to increased risk of suicidal thoughts or attempts.
+3. **Lithium**:
+   - Primarily used for bipolar disorder to stabilize mood and prevent manic episodes.
+   - Effective for long-term prevention of bipolar depressive episodes.
+   - Can be used as an adjunct treatment for depression.
+   - Reduces the risk of suicide and mortality in people with depression or bipolar disorder.
+   - May contribute to the treatment of substance use disorders in some people with bipolar disorder.
+   - Reduces the risk of dementia in people with bipolar disorder.
+   - Requires close monitoring of blood levels due to a narrow therapeutic index.
+4. **Other Treatments**:
+   - **Stimulants (e.g., amphetamine, modafinil)**: May be effective in the short term or as adjuvant therapy.
+   - **Folate Supplements**: May have a role in treating persistent depression symptoms.
+   - **Omega-3 Fatty Acids**: Insufficient high-quality evidence to suggest effectiveness in depression.
+   - **Vitamin D**: Limited evidence suggests it may alleviate symptoms in vitamin D-deficient individuals.
+   - **St. John's Wort**: More effective than placebo and as effective as standard antidepressants for mild to moderate depression.
+   - **Electroconvulsive Therapy (ECT), Ketamine, Esketamine, RTMS**: Effective for treatment-resistant depression.
+5. **Adjunctive Treatments**:
+   - **Low-Dose Thyroid Hormone**: May be added to existing antidepressants to treat persistent depression symptoms.
+   - **Atypical Antipsychotics (e.g., Aripiprazole)**: More effective than bupropion when added to SSRIs for treatment-resistant depression.
+In summary, while SSRIs and bupropion are commonly used for depression, lithium is a key treatment for bipolar disorder, with additional benefits in reducing suicide risk and dementia. Adjunctive treatments like bupropion, atypical antipsychotics, and thyroid hormone can enhance the effectiveness of primary treatments.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>The provided text discusses various treatments for depression, including antidepressants, mood stabilizers, and other medications. Here are some key points:
+1. **Bupropion**: Bupropion is effective in treating depression, especially in patients with seasonal affective disorder. It has a lower risk of sexual side effects and weight gain compared to other antidepressants.
+2. **SSRIs**: Selective serotonin reuptake inhibitors (SSRIs) are commonly prescribed for depression. They have a moderate effect size and are effective in treating moderate to severe depression.
+3. **Lithium**: Lithium is a mood stabilizer that is effective in treating bipolar disorder and major depressive disorder. It has a low therapeutic index, requiring close monitoring of blood levels.
+4. **Lamotrigine**: Lamotrigine is an anticonvulsant that is effective in treating bipolar disorder and unipolar depression. It has a lower risk of side effects compared to other mood stabilizers.
+5. **Other treatments**: Other treatments for depression include electroconvulsive therapy (ECT), ketamine, and esketamine. These treatments are effective for treatment-resistant depression.
+6. **Combination therapy**: Combination therapy, such as adding bupropion to an SSRI, can be effective in treating depression.
+7. **Vitamin D**: Vitamin D supplementation may be beneficial in alleviating symptoms of depression in individuals with vitamin D deficiency.
+8. **Omega-3 fatty acids**: Omega-3 fatty acids have limited evidence supporting their effectiveness in treating depression.
+9. **Statins**: Statins have been shown to have antidepressant effects and may be effective in preventing depression in some cases.
+10. **Folate supplements**: Folate supplements may have a role in treating depression, although the evidence is limited.
+Overall, the text highlights the importance of individualized treatment approaches for depression, taking into account the patient's specific needs and medical history.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -885,17 +1671,86 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Misoprostol</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Misoprostol</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Misoprostol</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Misoprostol</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Misoprostol</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Misoprostol</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the articles, it is clear that nonsteroidal anti-inflammatory drugs (NSAIDs) and aspirin have significant gastrointestinal (GI) side effects, which can be severe and even life-threatening. Misoprostol, while primarily used for medical abortions, also has gastrointestinal effects and can be used to mitigate the GI side effects of NSAIDs. Here's a summary of the key points:
+1. **NSAID Side Effects**:
+   - **Gastrointestinal Adverse Effects**: NSAIDs cause direct irritation of the gastric mucosa and reduce the levels of protective prostaglandins, leading to increased gastric acid secretion, diminished bicarbonate and mucus secretion, and reduced trophic effects on the epithelial mucosa.
+   - **Common Side Effects**: Nausea, vomiting, indigestion, gastric ulceration, bleeding, and diarrhea.
+   - **Risk Factors**: The risk of GI adverse effects increases with longer duration of therapy and higher doses. Certain NSAIDs, such as indomethacin, ketoprofen, and piroxicam, have higher rates of gastric adverse effects compared to ibuprofen and diclofenac.
+   - **Prevention**: Proton pump inhibitors (PPIs) and prostaglandin analogs like misoprostol can reduce the risk of GI ulcers, but these methods are expensive for long-term use.
+2. **Aspirin Side Effects**:
+   - **GI Effects**: Aspirin can cause similar GI side effects as other NSAIDs, including ulceration and bleeding.
+   - **Contraindications**: People with peptic ulcers, mild diabetes, gastritis, salicylate intolerance, asthma, and hyperuricemia should avoid aspirin.
+   - **Dengue Fever**: Aspirin is not recommended during dengue fever due to increased bleeding risk.
+3. **Misoprostol**:
+   - **Medical Abortion**: Misoprostol is used alone or in combination with mifepristone or methotrexate for medical abortions. It is less effective alone (88% success rate up to 8 weeks gestation) and can cause heavy bleeding in 1% of cases.
+   - **GI Effects**: Misoprostol can cause diarrhea, but higher doses can reduce the risk of gastric ulcers when used with NSAIDs.
+   - **Routes of Administration**: Vaginal and sublingual routes are more effective than oral administration due to bypassing the liver's first-pass effect.
+4. **Paracetamol (Acetaminophen)**:
+   - **Fever**: Paracetamol is used to reduce fever but its efficacy and benefits are unclear, especially in adults. It may not significantly affect mortality in febrile patients with stroke or sepsis.
+   - **Pain Relief**: Paracetamol is effective for mild to moderate pain but evidence for chronic pain is insufficient.
+   - **GI Effects**: While not as directly linked to GI side effects as NSAIDs, paracetamol can cause liver enzyme elevation, indicating potential liver damage.
+In summary, while NSAIDs and aspirin are effective for pain relief and reducing inflammation, they carry significant risks of GI side effects. Misoprostol can be used to mitigate these risks but also has its own set of side effects. Paracetamol is generally safer for the GI tract but has limitations in its efficacy and safety profile, particularly for fever and chronic pain.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Misoprostol</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Misoprostol</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>The text discusses the use of pain-relief medications, specifically nonsteroidal anti-inflammatory drugs (NSAIDs) and acetaminophen (paracetamol), in various medical contexts.
+For people over 65 years old, the balance between the benefits and potential adverse effects of NSAIDs has not been well determined. The text highlights the risks of gastrointestinal bleeding, ulcer perforation, and death associated with NSAID use, and notes that many of these events are avoidable.
+The text also discusses the use of misoprostol, a medication that can be used for medical abortions, either alone or in combination with other medications. Misoprostol is most effective when used in combination with methotrexate or mifepristone, and can be used to dilate the cervix in preparation for a surgical abortion.
+Regarding NSAIDs, the text notes that the main adverse drug reactions (ADRs) associated with their use relate to direct and indirect irritation of the gastrointestinal (GI) tract. Common GI side effects include nausea, vomiting, indigestion, gastric ulceration or bleeding, and diarrhea.
+The text also discusses the use of acetaminophen (paracetamol) for reducing fever, pain, and patent ductus arteriosus. However, it notes that the evidence for its use in these contexts is limited, and that its benefits are unclear.
+Overall, the text highlights the importance of carefully weighing the benefits and risks of pain-relief medications, particularly in vulnerable populations such as the elderly and those with certain medical conditions.
+Key points:
+* NSAIDs have a high risk of gastrointestinal bleeding, ulcer perforation, and death, particularly in older adults.
+* Misoprostol can be used for medical abortions, either alone or in combination with other medications.
+* Acetaminophen (paracetamol) has limited evidence for its use in reducing fever, pain, and patent ductus arteriosus.
+* The benefits of pain-relief medications must be carefully weighed against their potential risks, particularly in vulnerable populations.</t>
         </is>
       </c>
     </row>
@@ -915,17 +1770,78 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Vibrators</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Penile implants</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vacuum erection device</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Eroxon</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Eroxon</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>The treatment of erectile dysfunction (ED) has seen significant advancements over the years, with various methods and medications being introduced to address the condition. One of the most notable developments was the demonstration by British physiologist Giles Brindley in 1983, where he used papaverine injections to induce an erection, showcasing the potential of pharmacological treatments for ED. However, the most common treatment today is the oral phosphodiesterase type 5 (PDE5) inhibitor, sildenafil (Viagra), which was approved by the FDA in 1998 and quickly became the fastest-selling drug in history.
+Sildenafil works by inhibiting PDE5, which increases the levels of cyclic guanosine monophosphate (cGMP) in the corpus cavernosum, leading to smooth muscle relaxation and increased blood flow, resulting in an erection. Other PDE5 inhibitors include vardenafil (Levitra) and tadalafil (Cialis), all of which are available by prescription. As of 2018, sildenafil became available over-the-counter in the UK as Viagra Connect, allowing men to purchase it without a prescription after a consultation with a pharmacist.
+The use of sildenafil and other PDE5 inhibitors is not without risks. They can interact with certain medications, such as protease inhibitors used for HIV treatment, erythromycin, and cimetidine, leading to increased plasma levels and potential side effects. Additionally, the use of sildenafil with α1 blockers or nitric oxide donors can cause hypotension. Therefore, patients are advised to consult their healthcare providers before starting these medications.
+In cases where oral medications are not effective, other treatment options include penile injections, vacuum erection devices, and penile implants. Penile injections typically involve medications such as papaverine, phentolamine, and prostaglandin E1 (alprostadil). These injections can induce an erection within minutes and last for up to an hour. However, they can cause side effects such as priapism, a painful and potentially dangerous condition where an erection lasts for more than four hours.
+Vacuum erection devices are another non-invasive option. These devices use negative pressure to draw blood into the penis, creating an erection. Once the penis is engorged, a constriction band is placed around the base to maintain the erection. These devices are available by prescription and can be used just prior to sexual intercourse.
+For men with severe ED, penile implants may be considered. These are surgically implanted devices that provide a permanent solution to ED. There are two types of implants: inflatable and semi-rigid. Inflatable implants consist of two cylinders that are inserted into the penis, a pump, and a reservoir. When the pump is activated, the cylinders fill with fluid, creating an erection. Semi-rigid implants are less invasive and consist of two flexible rods that are inserted into the penis. These implants can be bent to create an erection.
+In addition to pharmacological and mechanical treatments, lifestyle changes and counseling can also be beneficial. Regular exercise, particularly aerobic exercise, can help prevent ED during midlife. Counseling can address psychological factors contributing to ED, such as stress and anxiety related to sex.
+In summary, the treatment of ED has evolved significantly, with oral medications like sildenafil being the most common first-line treatment. However, a variety of options are available, including injections, vacuum devices, and surgical interventions, to address the underlying causes of ED and improve sexual function.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Yohimbine</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>Vibrator</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Vibrator</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>The final answer is not a number, but rather a summary of the treatment options for erectile dysfunction (ED). Here is a summary:
+* Medications: PDE5 inhibitors (sildenafil, vardenafil, tadalafil), papaverine, phentolamine, and prostaglandin E1 (alprostadil) can be used to treat ED.
+* Vacuum erection devices: Can be used to help draw blood into the penis and maintain an erection.
+* Penile pumps: Can be used to help draw blood into the penis and maintain an erection.
+* Penile implants: Can be used to help maintain an erection.
+* Focused shockwave therapy: Can be used to improve blood flow to the penis and treat ED.
+* Testosterone replacement therapy: Can be used to treat low testosterone levels, which can contribute to ED.
+* Counseling: Can be used to address psychological causes of ED.
+* Lifestyle changes: Exercise, weight loss, and quitting smoking can help improve ED symptoms.
+It's worth noting that the most effective treatment for ED will depend on the underlying cause of the condition, and a healthcare professional should be consulted to determine the best course of treatment.</t>
         </is>
       </c>
     </row>
@@ -950,10 +1866,55 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Sevelamer</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sevelamer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sevelamer</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>sevelamer</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>sevelamer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>calcium carbonate</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>sevelamer</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Sevelamer</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Sevelamer</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Sevelamer</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Sevelamer</t>
         </is>
@@ -975,17 +1936,62 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Dexamethasone</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dexamethasone</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>ibuprofen</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ibuprofen</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ibuprofen</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Dexamethasone</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Ibuprofen</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Acetazolamide</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Ibuprofen</t>
         </is>
       </c>
     </row>
@@ -1010,12 +2016,57 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Endoscopic variceal ligation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Endoscopic variceal ligation</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Endoscopic variceal ligation</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>endoscopic variceal ligation</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>endoscopic variceal ligation</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>endoscopic variceal ligation</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>endoscopic variceal ligation</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Prophylactic endoscopic variceal ligation</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Endoscopic variceal ligation</t>
         </is>
       </c>
     </row>
@@ -1048,6 +2099,51 @@
           <t>Pyrazinamide</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrazinamide</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pyrazinamide</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pyrazinamide</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Pyrazinamide</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Pyrazinamide</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Pyrazinamide</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Pyrazinamide</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Pyrazinamide</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Pyrazinamide</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1070,12 +2166,67 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Procainamide</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Procainamide</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Procainamide</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>procainamide</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>procainamide</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>procainamide</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Based on the provided information, it appears that the treatment options for managing supraventricular tachycardia (SVT) have evolved with the advent of newer techniques such as systemoablation, particularly cryoablation. Cryoablation offers a safer alternative to radiofrequency ablation for SVT involving the atrioventricular (AV) node, as it reduces the risk of injuring the AV node, which could necessitate the implantation of a permanent pacemaker. This method involves cooling tissue to specific temperatures to either temporarily or permanently ablate problematic pathways, thereby providing a curative option for patients with AV nodal reentrant tachycardia (AVNRT) and other SVTs near the AV node.
+In the context of SVT, the atrioventricular node serves as a critical "gating mechanism" that regulates the transmission of electrical impulses from the atria to the ventricles, preventing excessively high heart rates from reaching the ventricles. However, in cases of SVT, an accessory pathway or an abnormal AV node function can bypass this protective mechanism, leading to rapid heart rates. Cryoablation offers a precise and reversible method to address these issues, making it particularly beneficial for young patients with mild but persistent symptoms who might otherwise be hesitant to undergo treatments with higher risks.
+Regarding the broader context of cardiovascular treatments, warfarin is a widely used anticoagulant for preventing blood clots in conditions such as atrial fibrillation, valvular heart disease, and after certain surgeries. However, its use requires careful monitoring due to the risk of bleeding and the need for dose adjustments based on genetic factors and interactions with other medications. Echocardiography plays a crucial role in diagnosing and managing various cardiac conditions, including valvular heart disease and congenital abnormalities, and is particularly valuable in pediatric cardiology and fetal cardiology.
+In the treatment of pulmonary embolism (PE), thrombolysis is recommended for massive PEs causing hemodynamic instability, while the use of inferior vena cava (IVC) filters is considered in specific scenarios where anticoagulation is contraindicated or ineffective. The evolving landscape of interventional cardiology includes techniques like catheter-directed thrombolysis and ultrasound-assisted thrombolysis, which offer promising alternatives for managing PE.
+Overall, these advancements in treatment options reflect the ongoing progress in cardiology, emphasizing the importance of precise, minimally invasive techniques and personalized approaches to managing cardiovascular conditions.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>Procainamide</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Procainamide</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Procainamide</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>The text discusses various medical conditions and treatments related to the heart, including supraventricular tachycardia (SVT), atrial fibrillation, and pulmonary embolism. Here are some key points mentioned in the text:
+1. **Supraventricular Tachycardia (SVT)**: SVT is a type of abnormal heart rhythm that can be treated with radiofrequency ablation or cryoablation. Cryoablation is a newer treatment that involves freezing the tissue to -10°C, which can be reversed if the wrong tissue is frozen.
+2. **Atrial Fibrillation**: Atrial fibrillation is a type of irregular heartbeat that can be treated with medications or cardioversion. Cardioversion involves using electrical shocks to restore a normal heartbeat.
+3. **Pulmonary Embolism**: Pulmonary embolism is a blockage of an artery in the lungs that can be caused by a blood clot. Treatment options include thrombolysis, catheter-directed thrombolysis, and inferior vena cava filter placement.
+4. **Warfarin**: Warfarin is an anticoagulant medication used to prevent blood clots. It works by blocking vitamin K epoxide reductase, an enzyme that reactivates vitamin K1.
+5. **Echocardiography**: Echocardiography is a medical imaging technique used to visualize the heart and its blood vessels. It is commonly used to diagnose and monitor heart conditions, including valvular heart disease and congenital abnormalities.
+Overall, the text highlights the importance of accurate diagnosis and treatment of heart conditions, and the need for ongoing research and development of new treatments and technologies.</t>
         </is>
       </c>
     </row>
@@ -1100,10 +2251,55 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>Propranolol</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>Labetalol</t>
         </is>
@@ -1130,12 +2326,100 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Azithromycin</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Azithromycin</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Azithromycin</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>azithromycin</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>azithromycin</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>azithromycin</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Based on the provided information, here are the key points regarding the use of doxycycline during pregnancy and lactation, and its application in pediatric cases:
+1. **FDA Classification and Pregnancy:**
+   - Doxycycline is categorized by the FDA as a Class D drug during pregnancy, indicating that there is evidence of risk to the fetus, but the benefits may outweigh the risks in certain situations.
+   - High doses of rifampicin (used in tuberculosis treatment) can cause neural tube defects in animals, but no such effect has been found in humans. However, caution is advised during pregnancy.
+2. **Breastfeeding:**
+   - Doxycycline crosses into breast milk, making it a concern during breastfeeding.
+   - Other tetracycline antibiotics are contraindicated in pregnancy and up to eight years of age due to the potential for disrupting bone and tooth development.
+3. **Dental Effects:**
+   - The FDA includes a class warning for all tetracyclines about staining of teeth (typically yellow to brown discoloration) and decreased development of dental enamel in children exposed to tetracyclines in utero, during breastfeeding, or during early childhood (under eight years of age).
+   - The best available evidence indicates that doxycycline has little or no effect on hypoplasia (underdevelopment) of dental enamel or on staining of primary teeth (baby teeth).
+4. **Pediatric Use:**
+   - The US Centers for Disease Control and Prevention (CDC) recommends the use of doxycycline for the treatment of Q fever and tick-borne rickettsial diseases in children of all ages.
+   - Some researchers advocate for the use of doxycycline in children with malaria as well.
+5. **Historical Context:**
+   - The earliest mentions of child-specific medical problems appear in the Hippocratic corpus and the Sacred Disease, discussing topics such as childhood epilepsy and premature births.
+   - Ancient Indian texts like the Sushruta Samhita and Kashyapa Samhita contain information about pediatrics.
+   - Byzantine physicians like Oribasius, Aetius of Amida, Alexander Trallianus, and Paulus Aegineta contributed to the field of pediatrics.
+   - Islamic Golden Age writers, such as Al-Razi, served as a bridge for Greco-Roman and Byzantine medicine and added ideas of their own, especially in pediatrics.
+6. **Syphilis Treatment:**
+   - Syphilis can be effectively treated with antibiotics, with benzathine benzylpenicillin being the preferred antibiotic for most cases, injected into a muscle.
+   - In those with a severe penicillin allergy, doxycycline or tetracycline may be used.
+   - During treatment, people may develop fever, headache, and muscle pains, known as a Jarisch-Herxheimer reaction.
+7. **Tuberculosis Management:**
+   - Adverse effects of individual anti-TB drugs are described, with the most common being thrombocytopenia (caused by rifampicin), neuropathy (caused by isoniazid), vertigo (caused by streptomycin), hepatitis (caused by pyrazinamide, rifampicin, and isoniazid), and rash (caused by pyrazinamide, rifampicin, and ethambutol).
+   - Pregnant women should be advised to avoid getting pregnant until TB treatment is completed, and aminoglycosides should be used with caution due to the potential for causing deafness in the unborn child.
+These points summarize the key aspects of doxycycline's use during pregnancy and lactation, its application in pediatric cases, and the historical context of pediatrics and syphilis treatment.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>Azithromycin</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Azithromycin</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Azithromycin</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Based on the provided text, here are some key points related to syphilis, tuberculosis, doxycycline, and pediatrics:
+1. **Syphilis**:
+	* Syphilis is a bacterial infection caused by Treponema pallidum.
+	* It can be transmitted through sexual contact, from mother to baby during pregnancy or at birth, and through other means.
+	* Diagnosis is typically made using blood tests or dark field microscopy.
+	* Treatment involves antibiotics, with benzathine benzylpenicillin being the preferred option.
+2. **Tuberculosis (TB)**:
+	* TB is a bacterial infection caused by Mycobacterium tuberculosis.
+	* Pregnancy itself is not a risk factor for TB, but untreated TB in pregnancy can lead to miscarriage and major fetal abnormalities.
+	* Rifampicin can make hormonal contraception less effective, and aminoglycosides may cause deafness in the unborn child.
+3. **Doxycycline**:
+	* Doxycycline is a tetracycline antibiotic used to treat various infections.
+	* It is categorized as a class D drug in pregnancy, meaning there is evidence of risk to the fetus but the benefits may outweigh the risks in certain situations.
+	* Doxycycline crosses into breast milk and is therefore a concern during breastfeeding.
+4. **Pediatrics**:
+	* The earliest mentions of child-specific medical problems appear in the Hippocratic Corpus, published in the 5th century BCE.
+	* Greek philosophers and physicians, such as Celsus, Soranus of Ephesus, and Galen, discussed specific illnesses affecting children in their works.
+	* The field of pediatrics has a rich history, with contributions from various cultures and civilizations.
+These points provide a brief overview of the topics mentioned in the provided text.</t>
         </is>
       </c>
     </row>
@@ -1155,17 +2439,92 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Tamoxifen</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Tamoxifen</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Aromatase inhibitors</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Exemestane</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Tamoxifen</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>The provided information highlights several key aspects of breast cancer, including its diagnosis, treatment, and research advancements. Here's a summary of the relevant points:
+### Diagnosis and Risk Factors
+- **Signs and Symptoms**: Include a lump in the breast, changes in breast shape, dimpling of the skin, nipple discharge, inverted nipple, and red or scaly patches of skin.
+- **Risk Factors**: Obesity, lack of physical exercise, alcohol consumption, hormone replacement therapy, radiation exposure, early menstruation, late childbirth, older age, prior breast cancer, and family history.
+- **Genetic Factors**: About 5-10% of cases are due to inherited genetic mutations, such as BRCA1 and BRCA2.
+- **Types of Breast Cancer**: Ductal and lobular carcinomas are common, with over 18 other subtypes.
+### Diagnosis and Staging
+- **Biopsy**: Confirms the diagnosis of breast cancer.
+- **Carcinoma in Situ**: Cells are cancerous but have not spread beyond their original location. Ductal carcinoma in situ (DCIS) and lobular carcinoma in situ (LCIS) are precancerous conditions.
+- **Grading**: Invasive tumor tissue is graded based on tubule formation, nuclear appearance, and mitotic rate.
+### Treatment
+- **Surgery**: Includes lumpectomy, mastectomy, and sentinel lymph node biopsy.
+- **Radiation Therapy**: Used after surgery to reduce the risk of recurrence.
+- **Chemotherapy**: Used to treat advanced or metastatic breast cancer.
+- **Hormonal Therapy**: Used for hormone receptor-positive breast cancer, including tamoxifen, raloxifene, and aromatase inhibitors.
+- **Targeted Therapy**: Includes trastuzumab for HER2-positive breast cancer, CDK4/6 inhibitors for ER-positive breast cancer, and PARP inhibitors for BRCA-mutated cancers.
+- **Immunotherapy**: Atezolizumab and pembrolizumab for specific genetic markers.
+### Prevention
+- **Chemoprevention**: Aromatase inhibitors and tamoxifen can reduce the risk of breast cancer in high-risk individuals.
+- **Surgical Prevention**: Bilateral mastectomy may be considered in high-risk women.
+### Research and Clinical Trials
+- **Targeted Therapies**: New drugs and combinations are being evaluated, such as ribociclib plus endocrine therapy.
+- **Immunotherapy**: Investigating the use of immune checkpoint inhibitors like atezolizumab and pembrolizumab.
+- **Gene Therapy**: Fenretinide is being studied for its potential to reduce breast cancer risk.
+- **Antibiotics**: Preoperative antibiotics may help prevent surgical site infections.
+### Metastatic Disease
+- **Common Sites**: Bones (67%), liver (41%), lungs (37%), brain (13%), and peritoneum (10%).
+- **Treatment Options**: Chemotherapy, endocrine therapy, HER2-targeted therapies, and bone-strengthening agents like denosumab and bisphosphonates.
+- **Specific Therapies**: CDK4/6 inhibitors, mTOR inhibitors, PI3K inhibitors, and PARP inhibitors for specific genetic mutations.
+### Summary
+Breast cancer is a complex disease with various subtypes and treatment options. Early detection through screening and understanding genetic risk factors are crucial. Advances in targeted therapies, immunotherapy, and gene-specific treatments offer hope for improved outcomes in both early-stage and metastatic breast cancer.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Aromatase inhibitors</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Aromatase inhibitors</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>Anastrozole</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Aromatase inhibitors (AIs) are a suitable treatment option for premenopausal women with hormone receptor-positive breast cancer.</t>
         </is>
       </c>
     </row>
@@ -1190,12 +2549,74 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>lorazepam</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>lorazepam</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>lorazepam</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Based on the provided articles, here are some key points related to the medication and treatment of psychosis and schizophrenia:
+1. **Antipsychotic Medication Choice**: The choice of antipsychotic medication is based on a balance of benefits, risks, and costs. It is debated whether typical or atypical antipsychotics are better as a class. Tentative evidence suggests that amisulpride, olanzapine, risperidone, and clozapine may be more effective for positive symptoms but come with more side effects. Typical antipsychotics have similar drop-out and symptom relapse rates to atypicals when used at low to moderate dosages.
+2. **Clozapine**: Clozapine is effective for treatment-resistant schizophrenia but carries the risk of agranulocytosis (a potentially serious side effect involving a lowered white blood cell count).
+3. **Side Effects**: Most people on antipsychotics experience side effects. Typical antipsychotics tend to have a higher rate of extrapyramidal side effects, while atypical antipsychotics are associated with weight gain, diabetes, and metabolic syndrome. Olanzapine is particularly noted for weight gain, while risperidone and quetiapine also contribute to weight gain.
+4. **Neurobiology of Psychosis**: Psychosis has traditionally been linked to overactivity of dopamine, particularly in the mesolimbic pathway. However, recent evidence suggests that neurodegenerative pathophysiology also plays a significant role. The endocannabinoid system and NMDA receptor dysfunction are also implicated in psychosis.
+5. **Ziprasidone**: Ziprasidone is an atypical antipsychotic used for schizophrenia and bipolar disorder. Common side effects include tremors, tics, dizziness, dry mouth, restlessness, nausea, and mild sedation. It is less likely to cause weight gain compared to other atypical antipsychotics.
+6. **Discontinuation of Antipsychotics**: Gradual withdrawal is recommended to avoid acute withdrawal syndrome or rapid relapse. Symptoms of withdrawal may include nausea, vomiting, loss of appetite, restlessness, increased sweating, and trouble sleeping. Rarely, discontinuation can result in psychosis or tardive dyskinesia.
+7. **Amitriptyline**: Amitriptyline should be used with caution in patients with epilepsy, impaired liver function, pheochromocytoma, urinary retention, prostate enlargement, hyperthyroidism, and pyloric stenosis. It may aggravate psychosis in patients with schizophrenia and precipitate mania in those with bipolar disorder.
+8. **Differential Diagnosis**: To diagnose schizophrenia, other causes of psychosis must be excluded. Conditions such as bipolar disorder, borderline personality disorder, substance intoxication, and delusional disorder can present with similar symptoms. A thorough medical and neurological examination may be necessary to rule out medical conditions that can produce psychotic symptoms.
+These points highlight the complexity of treating psychosis and schizophrenia, emphasizing the importance of careful medication management and thorough differential diagnosis.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>Clozapine</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Clozapine</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>The articles provided discuss various aspects of psychosis, including its treatment, neurobiology, and medication. Here are some key points that can be derived from the articles:
+1.  **Treatment of Psychosis**: The choice of antipsychotic medication depends on benefits, risks, and costs. Typical and atypical antipsychotics have different side effect profiles, with typical antipsychotics associated with extrapyramidal side effects and atypical antipsychotics associated with weight gain, diabetes, and metabolic syndrome.
+2.  **Neurobiology of Psychosis**: The dopamine hypothesis of psychosis suggests that overactivity of the dopamine system, particularly in the mesolimbic pathway, contributes to psychotic symptoms. However, this theory is not sufficient to explain all cases of psychosis, and other factors such as NMDA receptor dysfunction and endocannabinoid system dysregulation may also play a role.
+3.  **Medications for Psychosis**: Various medications are used to treat psychosis, including antipsychotics, mood stabilizers, and antidepressants. The choice of medication depends on the individual's symptoms, medical history, and response to previous treatments.
+4.  **Ziprasidone**: Ziprasidone is an atypical antipsychotic used to treat schizophrenia and bipolar disorder. It is available in oral and injectable forms and has a lower risk of weight gain compared to other atypical antipsychotics.
+5.  **Amitriptyline**: Amitriptyline is a tricyclic antidepressant that can be used to treat depression and certain types of pain. It has a range of side effects and should be used with caution in patients with certain medical conditions.
+6.  **Schizophrenia**: Schizophrenia is a chronic mental health disorder characterized by hallucinations, delusions, and disorganized thinking and behavior. It is essential to rule out other conditions that may cause similar symptoms, such as substance-induced psychosis or medical illnesses.
+7.  **Discontinuation of Antipsychotics**: When discontinuing antipsychotic medication, it is recommended to do so gradually to avoid acute withdrawal syndrome or rapid relapse. Symptoms of withdrawal may include nausea, vomiting, and loss of appetite.
+These articles provide a comprehensive overview of the treatment, neurobiology, and medication options for psychosis, as well as the importance of careful diagnosis and discontinuation of antipsychotic medication.</t>
         </is>
       </c>
     </row>
@@ -1228,6 +2649,51 @@
           <t>V/Q scan</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>V/Q scans</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1250,12 +2716,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>CTPA</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CTPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CTPA</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>CTPA</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>CT pulmonary angiogram</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>CT_pulmonary_angiogram</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>CT pulmonary angiogram</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>CT pulmonary angiogram (CTPA)</t>
         </is>
       </c>
     </row>
@@ -1288,6 +2799,67 @@
           <t>V/Q scan</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CTPA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>V/Q scans</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Based on the information provided, the patient's Wells score is 2.0 to 6.0, which indicates a moderate probability of pulmonary embolism (PE). The patient's score falls into the moderate risk category, which means there is a 29% chance of having a PE based on pooled data. Given this moderate probability, the next step would be to perform a D-dimer test. If the D-dimer test is negative, PE can be excluded. However, if the D-dimer test is positive, further imaging is required.
+In the context of pregnancy, the decision between a ventilation/perfusion (V/Q) scan and a CT pulmonary angiogram (CTPA) is critical. A V/Q scan involves less radiation to the fetus but more to the mother's breast tissue, while a CTPA involves more radiation to the mother's breast tissue but less to the fetus. Given the higher risk of radiation-induced breast cancer for the mother, the CTPA is generally preferred in suspected pulmonary embolism during pregnancy due to its higher sensitivity and specificity, despite the higher radiation dose to the mother's breast tissue.
+Therefore, the recommendation would be to perform a D-dimer test first. If the D-dimer is negative, PE can be excluded. If the D-dimer is positive, a CTPA would be the preferred imaging modality to diagnose or exclude PE, considering the higher sensitivity and specificity of CTPA, despite the radiation concerns. However, the decision should be made in consultation with a radiologist and the patient's obstetrician to weigh the risks and benefits of each imaging modality.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>V/Q scan</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>The Wells score is a clinical prediction rule used to determine the probability of deep vein thrombosis (DVT) or pulmonary embolism (PE) in patients. The score is calculated based on several clinical factors, including:
+* Clinically suspected DVT: 3.0 points
+* Alternative diagnosis is less likely than PE: 3.0 points
+* Tachycardia (heart rate &gt; 100): 1.5 points
+* Immobilization (≥ 3 days) / surgery in previous four weeks: 1.5 points
+* History of DVT or PE: 1.5 points
+* Hemoptysis: 1.0 point
+* Malignancy (with treatment within six months) or palliative: 1.0 point
+The score is then categorized as follows:
+* Score &gt; 6.0: High probability (59% based on pooled data)
+* Score 2.0 to 6.0: Moderate probability (29% based on pooled data)
+* Score &lt; 2.0: Low probability (15% based on pooled data)
+The Wells score is used in conjunction with other diagnostic tests, such as D-dimer and imaging studies, to determine the likelihood of DVT or PE.
+In the context of pulmonary embolism, the Wells score is used to determine the probability of PE in patients with suspected PE. A score of 4 or less indicates that PE is unlikely, and a D-dimer test may be used to rule out PE. A score of 5 or more indicates that PE is likely, and imaging studies, such as CT pulmonary angiography (CTPA), may be used to confirm the diagnosis.
+The use of the Wells score in conjunction with other diagnostic tests has been shown to improve the accuracy of diagnosis and reduce the need for unnecessary imaging studies.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1318,6 +2890,51 @@
           <t>Regadenoson</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>dobutamine</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1340,12 +2957,57 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>HIDA scan</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>HIDA scan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>HIDA scan</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>HIDA</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>HIDA scan</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>HIDA</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>HIDA scan</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>HIDA scan</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>HIDA scan</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>HIDA scan</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Cholescintigraphy</t>
         </is>
       </c>
     </row>
@@ -1375,7 +3037,52 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>MRE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>MRI</t>
         </is>
       </c>
     </row>
@@ -1405,6 +3112,51 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
           <t>Ultrasound</t>
         </is>
       </c>
@@ -1425,17 +3177,72 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Ultrasound</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>ultrasound</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ultrasound</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Based on the information provided, the standard treatment for acute appendicitis is surgical removal of the inflamed appendix, which can be performed through either an open laparotomy or a minimally invasive laparoscopic procedure. However, the diagnosis of appendicitis can sometimes be challenging, especially in children and women, due to the presence of other conditions that can mimic the symptoms of appendicitis.
+In children, conditions such as mesenteric adenitis, gastroenteritis, and intussusception can present with symptoms similar to appendicitis. In women, conditions like ectopic pregnancy, pelvic inflammatory disease, and ovarian torsion can also mimic appendicitis. Therefore, a thorough differential diagnosis is necessary to rule out these conditions before proceeding with surgery.
+Scoring systems like the Alvarado score and the Pediatric Appendicitis Score are used to help diagnose appendicitis, but their performance can be variable. In cases of equivocal scores, imaging studies such as CT scans or ultrasounds may be used to confirm the diagnosis and reduce the risk of negative appendectomies.
+CT scans are particularly useful in diagnosing appendicitis due to their high resolution and ability to visualize the appendix and surrounding tissues. They can also help identify complications such as abscess formation or perforation. However, CT scans involve radiation exposure, which is a consideration, especially in children and pregnant women.
+In summary, while surgical removal of the appendix is the standard treatment for appendicitis, accurate diagnosis is crucial to avoid unnecessary surgery and to manage other potential conditions that may present similarly. Imaging studies like CT scans play a vital role in confirming the diagnosis and guiding treatment decisions.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>The provided text discusses various aspects of appendicitis, including diagnosis, treatment, prognosis, and imaging studies. Here are the main points:
+1. **Diagnosis**: Appendicitis is diagnosed based on clinical presentation, laboratory tests, and imaging studies. Scoring systems, such as the Alvarado score, can help identify patients with appendicitis.
+2. **Treatment**: The standard treatment for acute appendicitis is surgical removal of the inflamed appendix, either through an open incision (laparotomy) or minimally invasive techniques (laparoscopy).
+3. **Prognosis**: Most people with appendicitis recover quickly after surgery, but complications can occur if treatment is delayed or if peritonitis occurs.
+4. **Imaging studies**: CT scanning is a useful diagnostic tool for appendicitis, offering advantages over traditional radiography, such as improved image resolution and the ability to visualize structures in multiple planes.
+5. **Kidney stone disease**: Imaging studies for kidney stone disease include traditional radiography (KUB), noncontrast helical CT scan, and ultrasound imaging. CT scan is the preferred diagnostic method for detecting kidney stones.
+The text also mentions various complications and conditions related to appendicitis, such as stump appendicitis, periappendicitis, and pseudoappendicitis. Additionally, it discusses the importance of prompt diagnosis and treatment to prevent complications and improve outcomes.</t>
         </is>
       </c>
     </row>
@@ -1465,7 +3272,58 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>CT myelography</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CT myelogram</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CT myelography</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CT myelogram</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>CT myelography</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Based on the provided information, Magnetic Resonance Angiography (MRA) is a non-invasive imaging technique used to visualize blood vessels in various parts of the body, including the cerebral and other vessels in the head and neck, the aorta and its branches in the thorax and abdomen, renal arteries, and arteries in the lower limbs. MRA is particularly useful for diagnosing conditions such as atherosclerosis, aneurysms, and abnormal vascular anatomy. 
+Compared to other imaging techniques, MRA has several advantages and disadvantages. One of its main advantages is that it is non-invasive, meaning no catheters need to be inserted into the body. Additionally, MRA does not expose the patient to ionizing radiation, unlike CT angiography and catheter angiography. Furthermore, the contrast media used in MRA are generally less toxic and pose a lower risk of allergic reactions compared to those used in CT angiography and catheter angiography. However, MRA is relatively expensive and has a lower spatial resolution compared to other imaging methods. Moreover, the examination time can be longer, and it is not suitable for patients with certain metal implants or pacemakers.
+For MRA procedures involving the cranial circulation, the process is similar to a standard MRI brain examination. The patient must remain still within the head coil, and the MRA typically adds about 10 minutes to the standard MRI protocol. However, MRA is contraindicated for patients with certain medical devices or metal objects in their body, such as pacemakers or metal fragments in the eyes, as these can interfere with the imaging process or pose a safety risk.
+In summary, MRA is a valuable diagnostic tool for visualizing blood vessels without the need for invasive procedures or ionizing radiation, but its use should be carefully considered based on the patient's specific medical condition and the availability of alternative imaging methods.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CT myelogram</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>CT myelogram</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>CT Myelogram</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>The text discusses the use of Magnetic Resonance Angiography (MRA) in diagnosing vascular diseases, particularly in the coronary arteries. It highlights the advantages of MRA over other imaging techniques, such as Computed Tomography (CT) angiography and invasive catheter angiography, including its non-invasive nature, lack of ionizing radiation, and lower toxicity of contrast media. However, it also notes the limitations of MRA, including its high cost, limited spatial resolution, and longer scanning time compared to CT. Additionally, MRA is not suitable for patients with certain medical conditions or implants, such as pacemakers or metal in the eyes or certain surgical clips.
+The text also discusses the use of MRA in visualizing cranial circulation, which requires the patient to be positioned similarly to a normal MRI brain examination. The procedure typically adds 10 minutes to the normal MRI protocol.
+In the context of Artificial Cardiac Pacemakers, the text explains the procedure of implanting a pacemaker, which involves inserting a pacing electrode into a chamber of the heart and connecting it to a pacemaker generator. It also discusses the different types of pacemakers, including single-chamber, dual-chamber, and biventricular pacemakers, as well as rate-responsive pacemakers.
+Overall, the text provides an overview of the use of MRA and pacemakers in medical imaging and treatment, highlighting their advantages and limitations.</t>
         </is>
       </c>
     </row>
@@ -1490,12 +3348,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>MRA</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>MRA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>MRA</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>MRA</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>CT myelography</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>MRA</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>MRI</t>
         </is>
       </c>
     </row>
@@ -1525,7 +3428,52 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>Noncontrast helical CT scan</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Noncontrast helical CT scan</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>MRI</t>
         </is>
       </c>
     </row>
@@ -1545,15 +3493,60 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Transesophageal echocardiogram</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Transesophageal echocardiogram</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Transesophageal echocardiogram</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>TEE</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>TEE</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>TEE</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Transesophageal echocardiogram</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Transesophageal Echocardiogram (TEE)</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>TEE</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>TEE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>TEE</t>
         </is>
@@ -1580,12 +3573,101 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Stress echocardiography</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>CCTA</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>CCTA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>CCTA</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Based on the provided information, here's a summary of the key points regarding Chronic Kidney Disease (CKD) and its diagnosis, prognosis, and management:
+### Diagnosis of CKD
+- **Initial Screening:** Blood tests to measure the estimated glomerular filtration rate (eGFR) and a urine test to measure albumin.
+- **Imaging and Biopsy:** Ultrasound or kidney biopsy may be performed to determine the underlying cause.
+- **Staging:** CKD is staged based on the severity of kidney function, with stages 1-5, where stage 5 indicates end-stage kidney disease (ESKD).
+### Prognosis of CKD
+- **Cardiovascular Risk:** CKD significantly increases the risk of cardiovascular disease, and patients with both CKD and cardiovascular disease have worse prognoses.
+- **Mortality:** CKD results in higher all-cause mortality, which increases as kidney function decreases.
+- **Risk Factors for Poor Prognosis:** Rapidly progressive CKD, uncontrolled hypertension, severe electrolyte abnormalities, structural kidney abnormalities, hereditary kidney disease, blood in the urine, recurrent severe kidney stones, and nephrotic syndrome.
+- **Survival Rates:** Kidney transplantation increases survival rates compared to other options, but it is associated with increased short-term mortality due to surgical complications.
+### Management of CKD
+- **Medications:** ACE inhibitors (ACEIs) or angiotensin II receptor antagonists (ARBs) are generally first-line agents for blood pressure control, as they slow the progression of kidney disease and reduce the risk of heart disease.
+- **Dietary Recommendations:** Adopting a healthy and diverse diet with a higher consumption of plant-based foods compared to animal-based foods and a lower consumption of ultraprocessed foods is recommended.
+- **Lifestyle Changes:** Staying active and adopting a healthy diet are key recommendations.
+- **Dialysis and Transplantation:** Severe CKD may require hemodialysis, peritoneal dialysis, or a kidney transplant for survival.
+- **Cancer Risk:** People with ESKD are at increased risk for cancer, particularly in younger individuals.
+### Contrast-Induced Nephropathy (CIN) Risk Factors
+- **Decreased Kidney Function:** Pre-existing decreased kidney function (eGFR &lt; 45 ml/min/1.73 m²) is a risk factor for CIN.
+- **Mehran Score:** A clinical prediction rule that includes factors such as systolic blood pressure, hematocrit levels, diabetes, and contrast media volume.
+- **Procedure-Related Risk Factors:** Large doses of contrast given intra-arterially, high osmolality contrast agents, and multiple contrast injections within 48-72 hours.
+### Cardiac Stress Test Utility
+- **ECG Treadmill Testing:** Recommended as the first choice for patients with medium risk of coronary heart disease based on risk factors such as smoking, family history, hypertension, diabetes, and high cholesterol.
+- **Perfusion Stress Test:** Appropriate for select patients, especially those with an abnormal resting electrocardiogram.
+- **Invasive Procedures:** Intracoronary ultrasound or angiogram can provide more information but are invasive and carry risks associated with cardiac catheterization.
+These points highlight the importance of early diagnosis, appropriate management, and lifestyle modifications in CKD, as well as the need for careful consideration of contrast use and cardiac stress testing in patients with kidney disease.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>CTA</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>The text does not provide a summary of the articles. However, I can provide a summary of the main points from each article:
+**Chronic Kidney Disease**
+* Chronic kidney disease (CKD) is a long-term kidney disease characterized by abnormal kidney function and/or structure.
+* Symptoms may include leg swelling, feeling tired, vomiting, loss of appetite, and confusion.
+* Complications include high blood pressure, insulin resistance, bone disease, and anemia.
+* Diagnosis is by blood tests to measure the estimated glomerular filtration rate (eGFR) and a urine test to measure albumin.
+* Treatment includes medications to lower blood pressure, blood sugar, and cholesterol, as well as lifestyle changes such as staying active and adopting a healthy diet.
+**Coronary Artery Disease**
+* The diagnosis of coronary artery disease (CAD) depends on the nature of the symptoms and imaging.
+* Non-invasive tests such as computed tomography angiography (CTA), positron emission tomography (PET), and stress echocardiography can diagnose CAD.
+* Invasive testing with coronary angiography (ICA) can be used when non-invasive testing is inconclusive or shows a high event risk.
+* The diagnosis of microvascular angina is a diagnosis of exclusion.
+**Contrast-Induced Nephropathy**
+* Contrast-induced nephropathy (CIN) is a type of kidney damage caused by the use of contrast agents during medical imaging procedures.
+* Risk factors for CIN include decreased kidney function, age, and certain medical conditions.
+* The Mehran score is a clinical prediction rule to estimate the probability of CIN.
+* Other factors that increase the risk of CIN include large doses of contrast, use of contrast agents with high osmolality, and multiple contrast injections within 48-72 hours.
+**Cardiac Stress Test**
+* The American Heart Association recommends electrocardiogram (ECG) treadmill testing as the first choice for patients with medium risk of coronary heart disease.
+* Perfusion stress test (with 99mTc labelled sestamibi) is appropriate for select patients, especially those with an abnormal resting electrocardiogram.
+* Intracoronary ultrasound or angiogram can provide more information but is invasive and carries the risk of complications associated with cardiac catheterization procedures.</t>
         </is>
       </c>
     </row>
@@ -1605,15 +3687,60 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>MRI</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>MRI</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Dual Energy CT</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>MRI</t>
         </is>
@@ -1635,17 +3762,121 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>CT scan</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CT scan</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>CT angiography</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CT angiography</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the articles, the management of an abdominal aortic aneurysm (AAA) involves several key points:
+1. **Treatment Options for Asymptomatic AAA:**
+   - **Conservative Management:** This involves monitoring the aneurysm without immediate surgical intervention.
+   - **Surveillance:** Regular monitoring to assess the aneurysm's size and growth rate.
+   - **Immediate Repair:** Surgical intervention if the aneurysm meets certain criteria.
+2. **Criteria for Repair:**
+   - **Growth Rate:** An aneurysm that grows more than 1 cm per year.
+   - **Size:** An aneurysm larger than 5.5 cm in males and 5.0 cm in females.
+   - **Symptoms:** Repair is indicated for symptomatic aneurysms.
+3. **Repair Methods:**
+   - **Open Aneurysm Repair:** Traditional surgical approach.
+   - **Endovascular Aneurysm Repair (EVAR):** Less invasive method, often associated with lower short-term mortality and shorter hospital stays.
+4. **Survival Rates:**
+   - Ten years after open AAA repair, the overall survival rate is 59%.
+5. **Screening Recommendations:**
+   - In the United States, screening with abdominal ultrasound is recommended for males aged 65 to 75 with a history of smoking.
+   - In the United Kingdom and Sweden, screening all men over 65 is recommended.
+6. **Risk Factors:**
+   - Smoking, high blood pressure, heart or blood vessel diseases, and genetic conditions like Marfan syndrome and Ehlers-Danlos syndrome.
+7. **Risks and Complications:**
+   - Rupture of an AAA can be life-threatening, with symptoms including abdominal or back pain, low blood pressure, and loss of consciousness.
+   - The risk of rupture increases with aneurysm size: below 5.5 cm, the risk is below 1% per year; between 5.5 and 7 cm, the risk is about 10% per year; and above 7 cm, the risk is about 33% per year.
+8. **Research and Future Directions:**
+   - There is ongoing research into biomechanics-based approaches to rupture risk assessment and the development of more accurate predictive models.
+   - Novel techniques like patient-specific anatomically correct AAA replicas and advanced material analogues are being developed for experimental models.
+   - Animal studies have shown potential targets for prevention and treatment, such as eliminating the gene for cyclophilin A (CypA) and targeting granzyme B (Gzmb).
+9. **CT Scan Utilization:**
+   - CT scans are increasingly used in emergency departments for diagnostic purposes, with variations in usage rates among different physicians.
+   - The increased use of CT scans has been particularly notable in pediatric populations and in screening adults for various conditions.
+In summary, the management of AAA involves a combination of surveillance, surgical intervention when necessary, and ongoing research to improve diagnostic and treatment methods.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>CT scan</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>CT scan</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>Computed Tomography Angiography (CTA)</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>The text discusses various topics related to abdominal aortic aneurysm (AAA), CT scans, and their applications. Here are some key points:
+**Abdominal Aortic Aneurysm (AAA)**
+* An AAA is a localized enlargement of the abdominal aorta that is greater than 3 cm in diameter or more than 50% larger than normal.
+* Symptoms are usually absent, but may include abdominal, back, or leg pain.
+* Large aneurysms can be felt by pushing on the abdomen.
+* Rupture may result in pain, low blood pressure, or loss of consciousness, and often leads to death.
+* Risk factors include smoking, high blood pressure, and other heart or blood vessel diseases.
+* Genetic conditions such as Marfan syndrome and Ehlers-Danlos syndrome increase the risk.
+* Screening with abdominal ultrasound is recommended for males between 65 and 75 years of age with a history of smoking.
+**Treatment and Repair**
+* Treatment options include conservative management, surveillance, and immediate repair.
+* Two modes of repair are available: open aneurysm repair and endovascular aneurysm repair (EVAR).
+* Repair is recommended if the aneurysm grows more than 1 cm per year or is bigger than 5.5 cm.
+* EVAR has a lower risk of death in the short term and a shorter hospital stay, but may not always be an option.
+**CT Scans**
+* CT scanning has several advantages over traditional two-dimensional medical radiography, including:
+	+ Elimination of superimposition of images of structures outside the area of interest.
+	+ Greater image resolution, enabling examination of finer details.
+	+ Ability to distinguish between tissues that differ in radiographic density by 1% or less.
+	+ Multiplanar reformatted imaging, allowing visualization in the transverse, coronal, or sagittal plane.
+* CT scanning can perform virtual colonoscopy with greater accuracy and less discomfort for the patient than a traditional colonoscopy.
+**Prevalence and Use of CT Scans**
+* An estimated 72 million CT scans were performed in the United States in 2007, accounting for close to half of the total per-capita dose rate from radiologic and nuclear medicine procedures.
+* Six to eleven percent of CT scans are done in children, an increase of seven to eightfold from 1980.
+* Similar increases have been seen in Europe and Asia.
+* The increased use of CT scans has been the greatest in two fields: screening of adults and CT imaging of children.
+**Research and Development**
+* Researchers are developing new endovascular devices that can treat more complex and tortuous anatomies.
+* Animal studies have shown that removing a single protein prevents early damage in blood vessels from triggering a later-stage, frequently lethal complication.
+* Elimination of the gene for a signaling protein called cyclophilin A (CypA) from a strain of mice provides complete protection against abdominal aortic aneurysm.
+* Other recent research has identified granzyme B (GZMB) as a potential target in the treatment of abdominal aortic aneurysms.</t>
         </is>
       </c>
     </row>
@@ -1678,6 +3909,51 @@
           <t>MRE</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>MRE</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>MRE</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>MRE</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>MRE</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>MRE</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>MRE</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>MRE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>MRE</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1708,6 +3984,51 @@
           <t>MRI</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1738,6 +4059,51 @@
           <t>Upper GI series</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Upper GI series</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Upper GI series</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Upper GI series</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Upper GI series</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Upper gastrointestinal series</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Upper GI series</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Upper GI series</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Upper GI series</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Upper GI series</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1760,10 +4126,55 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>CT scan</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CT scan</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CT scan</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CT scan</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
@@ -1790,10 +4201,55 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>ultrasound</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ultrasound</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ultrasound</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ultrasound</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>Ultrasound</t>
         </is>
@@ -1820,12 +4276,57 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Doppler ultrasound</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Doppler ultrasound</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Doppler ultrasound</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>MRI</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>MRI (Magnetic Resonance Imaging) venography.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Doppler ultrasound</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Doppler ultrasound</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>Venography</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Doppler ultrasound</t>
         </is>
       </c>
     </row>
@@ -1845,17 +4346,73 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>MRI</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>MRI</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>MRI</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Contrast agents used in X-ray radiography or CT scans can cause anaphylactoid reactions in approximately 0.03 – 0.1% of cases. Gadolinium-based contrast agents, however, have a lower incidence of nephrotoxicity compared to iodinated agents, making them a viable option for patients with renal impairment who would otherwise be unable to undergo contrast-enhanced CT scans. Gadolinium-based contrast agents are typically octadentate complexes of gadolinium (III), with a very stable complex (log K &gt; 20) that ensures the concentration of un-complexed Gd3+ ions remains below the toxicity limit. The 9th place in the metal ion's coordination sphere is occupied by a water molecule, which exchanges rapidly with water molecules in the agent's immediate environment, affecting the magnetic resonance relaxation time.
+In December 2017, the FDA announced new warnings for gadolinium-based contrast agents (GBCAs) due to the risk of a rare but serious illness, nephrogenic systemic fibrosis (NSF), particularly in patients with severe kidney failure requiring dialysis. Although gadolinium agents have been beneficial for patients with kidney impairment, the risk of NSF is associated with certain gadolinium-containing agents, with gadodiamide being the most frequently linked. Current guidelines in the United States recommend that dialysis patients should only receive gadolinium agents when essential and that dialysis should be performed as soon as possible after the scan.
+Contrast-induced nephropathy (CIN) is a risk factor for patients with decreased kidney function, especially those with an estimated glomerular filtration rate (eGFR) &lt; 45 ml/min/1.73 m² before intra-arterial administration with first-pass renal exposure or eGFR &lt; 30 ml/min/1.73 m² before intravenous administration or intra-arterial administration with second-pass renal exposure. The Mehran score is a clinical prediction rule to estimate the probability of CIN, which includes factors such as systolic blood pressure, age, hematocrit level, diabetes mellitus, contrast media volume, and decreased kidney function.
+Chronic kidney disease (CKD) stages are defined based on glomerular filtration rate (GFR) and the presence of kidney damage. Stage 1 indicates slightly diminished function with normal or relatively high GFR (≥90 ml/min/1.73 m²) and persistent albuminuria. Stage 2 involves mild reduction in GFR (60-89 ml/min/1.73 m²) with kidney damage. Stage 3 includes moderate reduction in GFR (30-59 ml/min/1.73 m²), with British guidelines distinguishing between stages 3a (GFR 45-59) and 3b (GFR 30-44). Stage 4 involves severe reduction in GFR (15-29 ml/min/1.73 m²), and Stage 5 is characterized by established kidney failure (GFR &lt; 15 ml/min/1.73 m²) requiring kidney replacement therapy.
+Imaging studies for kidney stone disease include ultrasound, CT scans, and MRI. Ultrasound is useful for detecting stones in children or pregnant women due to the absence of radiation exposure. However, CT scans remain the preferred initial diagnostic evaluation for urolithiasis due to their high sensitivity and specificity.
+For hepatocellular carcinoma (HCC), imaging modalities such as ultrasound, CT scans, and MRI are used to evaluate the liver. MRI has the advantage of delivering high-resolution images without ionizing radiation and is more sensitive and specific than CT in cirrhotic patients. Gadolinium contrast-enhanced and diffusion-weighted imaging can further increase sensitivity. MRI is particularly useful for differentiating HCC from regenerative nodules in cirrhotic patients. The Liver Imaging Reporting and Data System (LI-RADS) is a standardized system for reporting suspicious liver lesions and providing an estimated likelihood of malignancy.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>MRA</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>The text discusses various medical imaging techniques and their applications in diagnosing and treating different conditions. Here are the main points:
+1. **Contrast agents**: The text explains that contrast agents are used to shorten T2 and T2* in healthy tissue, reducing its signal intensity. The most commonly used intravenous contrast agents are based on chelates of gadolinium, which is highly paramagnetic.
+2. **Kidney function**: The text discusses the Mehran score, a clinical prediction rule to estimate the probability of contrast-induced nephropathy (CIN). The score includes various risk factors, such as systolic blood pressure, age, diabetes mellitus, and contrast media volume.
+3. **Chronic kidney disease (CKD)**: The text explains the stages of CKD, which are classified based on the glomerular filtration rate (GFR). Stage 1 is normal kidney function with kidney damage, while stage 5 is established kidney failure.
+4. **Kidney stone disease**: The text discusses the use of ultrasound imaging in detecting kidney stones, particularly in situations where X-rays or CT scans are discouraged.
+5. **Hepatocellular carcinoma (HCC)**: The text explains the imaging techniques used to evaluate the liver for HCC, including ultrasound, CT scan, and MRI. It also discusses the sensitivity and specificity of these techniques in detecting HCC.
+Overall, the text highlights the importance of accurate imaging techniques in diagnosing and treating various medical conditions.</t>
         </is>
       </c>
     </row>
@@ -1875,15 +4432,60 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>MRI</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>MRI</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>MRI</t>
         </is>
@@ -1905,17 +4507,83 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>Amoxicillin</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Amoxicillin</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Amoxicillin</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>doxycycline</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>amoxicillin</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>amoxicillin</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the articles, here's a summary of the key points related to tick bites, Lyme disease, and the use of doxycycline and amoxicillin:
+### Tick Bite Removal and Prevention
+- **Tick Removal**: Use fine-tipped tweezers to grasp the tick as close to the skin's surface as possible and pull upward with steady, even pressure. Avoid twisting or jerking the tick as this can cause the mouthparts to break off and remain in the skin. Do not use your fingers, nail polish, petroleum jelly, or heat to remove the tick.
+- **Preventive Antibiotics**: If a deer tick is found attached for 36 hours or more, a single dose of doxycycline may be administered within 72 hours of removal to reduce the risk of Lyme disease. However, this is not generally recommended for all people bitten, as the risk of infection is rare.
+### Doxycycline
+- **Medical Uses**: Doxycycline is used to treat Lyme disease, particularly when the patient presents with erythema migrans (EM) rash. The optimal duration of treatment is uncertain, but a 7-day course may be effective. Guidelines vary, with some recommending a 10-day course and others suggesting a 14-day course.
+- **Research**: Doxycycline is used as a research reagent in biomedical experiments due to its ability to disrupt protein translation in bacteria and eukaryotic cells. It is also used in tetracycline-controlled transcriptional activation systems to regulate gene expression.
+### Amoxicillin
+- **Medical Uses**: Amoxicillin is used to treat various conditions, including acute otitis media, respiratory infections, and H. pylori infections. It is also effective for the treatment of early cutaneous Lyme borreliosis.
+- **Lyme Disease**: Amoxicillin is effective for treating early cutaneous Lyme borreliosis, but its effectiveness and safety are neither better nor worse than other commonly used antibiotics.
+### Lyme Disease
+- **Early Localized Infection**: Approximately 80% of Lyme infections begin with a rash (erythema migrans) at the site of a tick bite. The rash usually appears 1-2 weeks after the bite and can expand to a diameter of 5-70 cm. The rash may be circular or oval, red or bluish, and may form a "bull's eye" pattern. It is often accompanied by flu-like symptoms such as fatigue, headache, body aches, fever, and chills.
+- **Symptoms**: Not everyone with Lyme disease has all symptoms, and many symptoms can also occur with other diseases, making diagnosis challenging.
+### Summary
+- **Tick Bite Management**: Proper removal of ticks and consideration of preventive antibiotics if the tick has been attached for 36 hours or more.
+- **Lyme Disease Treatment**: Doxycycline is the preferred treatment for Lyme disease, especially for early cutaneous Lyme borreliosis. Amoxicillin is also effective but is not typically the first-line treatment.
+- **Research and Clinical Use**: Doxycycline is widely used in research and clinical settings for its antimicrobial properties and gene expression regulation capabilities.
+This information highlights the importance of proper tick bite management and the role of antibiotics like doxycycline and amoxicillin in the treatment of Lyme disease.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Amoxicillin</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>The text discusses the treatment and prevention of Lyme disease, a tick-borne illness caused by the bacterium Borrelia burgdorferi. The text highlights the importance of prompt removal of the tick, as the risk of infectious transmission increases with the duration of tick attachment. It recommends using a single dose of doxycycline within 72 hours after removal of the tick to reduce the risk of Lyme disease, especially if the tick has been attached for 36 hours or is engorged.
+The text also discusses the use of doxycycline as a research reagent in biomedical research experiments, where it is used to regulate transgene expression in organisms and cell cultures. Additionally, it highlights the potential use of doxycycline in treating various medical conditions, including macular degeneration, rheumatoid arthritis, and Lyme disease.
+In terms of dosing, the text notes that the optimal dosing and duration of treatment for Lyme disease is a topic of ongoing research. It recommends a 10- to 14-day course of doxycycline for patients presenting with erythema migrans, but notes that the optimal duration of treatment remains uncertain.
+The text also discusses the use of amoxicillin in treating various conditions, including acute otitis media, respiratory infections, and Lyme disease. It notes that amoxicillin is effective in treating early cutaneous Lyme borreliosis and is often used in combination with other antibiotics to treat H. pylori infections.
+Overall, the text highlights the importance of prompt treatment and prevention of Lyme disease, as well as the potential use of doxycycline and amoxicillin in treating various medical conditions.</t>
         </is>
       </c>
     </row>
@@ -1948,6 +4616,51 @@
           <t>Propylthiouracil</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>PTU</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>propylthiouracil</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Thiouracil</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Propylthiouracil</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1970,12 +4683,79 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>Vitamin K antagonists</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>Warfarin</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Vitamin K antagonists</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the articles, here's a summary of key points related to stroke, atrial fibrillation, and artificial cardiac pacemakers:
+### Stroke
+- **Systemic Embolism**: A stroke can be caused by an embolism, which is a blockage in an artery due to a traveling particle or debris. Common sources of emboli include thrombi, fat, air, cancer cells, or clumps of bacteria.
+- **Risk Factors**: High-risk factors for stroke related to the heart include atrial fibrillation, rheumatic heart disease, artificial heart valves, and certain types of endocarditis. Low-risk factors include conditions like patent foramen ovale (PFO) and calcification of the mitral valve annulus.
+- **Prevention**: Blood pressure control and anticoagulation are recommended for stroke prevention. Warfarin and newer anticoagulants like dabigatran are commonly used for atrial fibrillation patients.
+- **Carotid Artery Stenosis**: If carotid artery stenosis is detected, carotid endarterectomy may be considered to reduce the risk of recurrent stroke.
+### Atrial Fibrillation (AF)
+- **Characteristics**: AF is an irregular and rapid heart rhythm originating in the atria, often starting as short episodes that can become longer or continuous over time.
+- **Symptoms**: Symptoms may include palpitations, fainting, lightheadedness, loss of consciousness, or shortness of breath.
+- **Complications**: AF is associated with an increased risk of heart failure, dementia, and stroke.
+- **Risk Factors**: High blood pressure, valvular heart disease, heart failure, coronary artery disease, cardiomyopathy, COPD, obesity, sleep apnea, alcohol intake, smoking, diabetes, and thyroid disorders.
+- **Diagnosis**: AF is diagnosed through an electrocardiogram (ECG) showing irregularly spaced QRS complexes without P waves.
+- **Management**: Treatment options include rate control (slowing heart rate) and rhythm control (restoring normal sinus rhythm).
+### Artificial Cardiac Pacemaker
+- **Complications**: Potential complications include infection, allergic reactions, swelling, bruising, bleeding, and pacemaker-mediated tachycardia (PMT).
+- **PMT**: PMT is a form of reentrant tachycardia where the pacemaker forms part of the circuit. It can be treated by reprogramming the pacemaker.
+- **Thromboembolic Events**: Pacemaker leads can disrupt blood flow and potentially cause thrombus formation, necessitating anticoagulation therapy.
+- **Lead Damage**: Pacemaker leads can damage the tricuspid valve over time, leading to tricuspid regurgitation and right-sided heart failure.
+- **Lead Removal**: Leads may need to be removed due to infection or degradation. Removal can be done by inserting new leads without removing old ones (not recommended) or by removing old leads and inserting new ones.
+These summaries highlight the interconnectedness of heart conditions, stroke risk, and the management of cardiac devices like pacemakers.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>The text discusses embolic stroke, which is a type of stroke caused by a blockage of an artery by an embolus, a traveling particle or debris in the arterial bloodstream. The embolus can originate from elsewhere in the body, such as the heart, and can be a thrombus, air, cancer cells, or clumps of bacteria. The symptoms of an embolic stroke are usually sudden and maximal at the start, and may be transient as the embolus is partially resorbed and moves to a different location or dissipates altogether.
+The text also discusses atrial fibrillation, a type of abnormal heart rhythm characterized by rapid and irregular beating of the atrial chambers of the heart. Atrial fibrillation is associated with an increased risk of heart failure, dementia, and stroke, and is often treated with medications to slow the heart rate or convert the rhythm to normal sinus rhythm.
+Additionally, the text mentions artificial cardiac pacemakers, which are medical devices that regulate the heartbeat. Complications from having surgery to implant a pacemaker can include infection, allergic reaction, swelling, bruising, or bleeding at the generator site, or around the heart. The leads of the pacemaker can also cause complications, such as thromboembolic events, damage to the tricuspid valve leaflets, and the need for lead removal.
+Overall, the text provides information on various cardiovascular conditions, including embolic stroke, atrial fibrillation, and artificial cardiac pacemakers, and discusses their symptoms, causes, and complications.</t>
         </is>
       </c>
     </row>
@@ -2000,12 +4780,57 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>Tenofovir</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tenofovir</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tenofovir</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>emtricitabine</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Tenofovir</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>emtricitabine</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>emtricitabine</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Dolutegravir</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tenofovir</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>DTG</t>
         </is>
       </c>
     </row>
@@ -2038,6 +4863,51 @@
           <t>Carbamazepine</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbamazepine</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Carbamazepine</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Carbamazepine</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Carbamazepine</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Carbamazepine</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Carbamazepine</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Carbamazepine</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Carbamazepine</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Carbamazepine</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2060,12 +4930,89 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>Glucocorticoids</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Glucocorticoids</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Glucocorticoids</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>glucocorticoids</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>glucocorticoids</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
           <t>Colchicine</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Based on the information provided, here are the key points regarding the use of nonsteroidal anti-inflammatory drugs (NSAIDs) and their management in the context of gout and rheumatoid arthritis (RA):
+1. **NSAIDs and Gout:**
+   - NSAIDs are used with caution in people over 50 years old and those with a family history of gastrointestinal (GI) problems.
+   - NSAIDs can be used during an acute attack of gout, but starting allopurinol during an attack is acceptable despite historical recommendations against it.
+   - NSAIDs should be used cautiously in individuals with cardiovascular, renal, or GI issues.
+   - NSAIDs can cause gastric ulcers, and misoprostol is sometimes co-prescribed with NSAIDs to prevent this adverse effect.
+2. **NSAIDs and Rheumatoid Arthritis (RA):**
+   - NSAIDs are used to reduce pain and stiffness in RA but do not affect the underlying disease course.
+   - NSAIDs are not first-line agents for RA management anymore.
+   - NSAIDs should be used cautiously in individuals with GI, cardiovascular, or renal problems.
+   - Methotrexate can be safely used in combination with NSAIDs if adequate monitoring is done.
+   - COX-2 inhibitors like celecoxib are equally effective as traditional NSAIDs.
+   - Paracetamol is an alternative for pain relief but may be associated with ulcer development.
+   - Physical therapy is an effective aid in pain management alongside regular rheumatic therapy.
+3. **Misoprostol and NSAIDs:**
+   - Misoprostol is used to prevent NSAID-induced gastric ulcers.
+   - Misoprostol acts on gastric parietal cells to inhibit gastric acid secretion.
+   - Omeprazole is considered more effective and better tolerated than misoprostol for preventing NSAID-induced ulcers.
+   - Misoprostol is sometimes co-prescribed with NSAIDs to prevent gastric ulcers.
+4. **NSAID Contraindications:**
+   - NSAIDs should be used with caution in individuals with a history of GI problems or those who have had previous GI issues from NSAID use.
+   - NSAIDs should be used cautiously in individuals with cardiovascular, renal, or GI issues.
+5. **Alternative Pain Management:**
+   - Neuromodulator agents like topical capsaicin may be used to reduce pain.
+   - Physical therapy is an effective aid in pain management for RA.
+   - Weak oral opioids may be used, but their adverse effects may outweigh the benefits.
+6. **Combination Therapy:**
+   - Methotrexate can be safely used in combination with NSAIDs if adequate monitoring is done.
+   - Clopidogrel can be used in combination with aspirin for the prevention of thrombosis after placement of a coronary stent or as an alternative antiplatelet drug for people intolerant to aspirin.
+7. **Proton Pump Inhibitors (PPIs) and NSAIDs:**
+   - PPIs can be used to prevent NSAID-induced ulcers.
+   - There are concerns about the interaction between clopidogrel and PPIs, which may affect the efficacy of clopidogrel.
+These points summarize the key considerations and recommendations for the use of NSAIDs in managing gout and RA, along with the precautions and alternative treatments available.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>Glucocorticoids</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Glucocorticoids</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Glucocorticoids</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>The final answer is: $\boxed{6}$</t>
         </is>
       </c>
     </row>
@@ -2098,6 +5045,66 @@
           <t>Hydroxychloroquine</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydroxychloroquine</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>sulfasalazine</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>hydroxychloroquine</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Hydroxychloroquine</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Based on the provided information, here are the key points regarding the use of methotrexate during pregnancy and its medical uses:
+### Methotrexate During Pregnancy
+- **Abortifacient**: Methotrexate is used to terminate pregnancies, particularly in cases of ectopic pregnancy or molar pregnancy.
+- **Molar Pregnancy Treatment**: Methotrexate is used in combination with dilation and curettage to treat molar pregnancies.
+- **Intrauterine Pregnancy Termination**: Rarely, methotrexate is used in combination with misoprostol to terminate intrauterine pregnancies.
+- **Monitoring**: Routine monitoring of complete blood count, liver function tests, and creatinine levels is recommended during methotrexate treatment.
+- **Folic Acid Co-Prescription**: Folic acid is commonly prescribed alongside methotrexate to minimize the risk of adverse effects.
+### Medical Uses of Methotrexate
+- **Chemotherapy**: Methotrexate is used in the treatment of various cancers, including solid tumors and hematological malignancies.
+- **Autoimmune Disorders**: Methotrexate is used to treat several autoimmune diseases, such as rheumatoid arthritis, psoriasis, psoriatic arthritis, and others.
+- **Rheumatoid Arthritis**: Methotrexate is a first-line therapy for rheumatoid arthritis, with weekly doses of 5-25 mg showing benefits for 12-52 weeks.
+- **Combination Therapy**: Methotrexate is often used in combination with other drugs, such as NSAIDs, sulfasalazine, and hydroxychloroquine.
+- **Ulcerative Colitis**: Methotrexate in combination with anti-TNF agents is effective for treating ulcerative colitis.
+- **Other Conditions**: Methotrexate is occasionally used for multiple sclerosis and systemic lupus erythematosus, with tentative evidence supporting its use.
+### Summary
+Methotrexate is a versatile drug with significant therapeutic benefits in both oncology and autoimmune disorders. However, its use during pregnancy is highly restricted and primarily limited to medical termination of pregnancy and treatment of specific pregnancy-related conditions. In non-pregnant patients, methotrexate is a cornerstone in the management of autoimmune diseases, particularly rheumatoid arthritis, and is often used in combination with other medications to enhance efficacy and manage side effects.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Hydroxychloroquine</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Prednisolone, Hydroxychloroquine, Sulfasalazine</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Hydroxychloroquine</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>The final answer is: There is no final answer to this question as it is a collection of text from various articles related to methotrexate and rheumatoid arthritis.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2115,17 +5122,62 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>Isavuconazole</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Isavuconazole</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>Insufficient evidence</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Isavuconazole</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>voriconazole</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>voriconazole</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>voriconazole</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>voriconazole</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Isavuconazole</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Liposomal amphotericin B</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>Voriconazole</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Itraconazole</t>
         </is>
       </c>
     </row>
@@ -2150,10 +5202,55 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>Xanthine stones</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Xanthine stones</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Xanthic urolithiasis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Xanthine stones</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>Xanthine</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Xanthine</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Xanthine</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Xanthine stones</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Xanthic urolithiasis</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Xanthic urolithiasis</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
         <is>
           <t>Xanthic urolithiasis</t>
         </is>
@@ -2175,15 +5272,60 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>Secukinumab</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Secukinumab</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Secukinumab</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>methotrexate</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>secukinumab</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>secukinumab</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>secukinumab</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Biosimilars</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Secukinumab</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Secukinumab</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t>Secukinumab</t>
         </is>
@@ -2218,6 +5360,51 @@
           <t>Cholestyramine</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>UDCA</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2235,17 +5422,72 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Sulfasalazine</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>Methotrexate</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sulfasalazine</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>methotrexate</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>sulfasalazine</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>leflunomide</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>**Summary of Methotrexate's Role in Treating Crohn's Disease:**
+Methotrexate, an immune-suppressant and chemotherapy agent, is used to manage autoimmune diseases, including Crohn's disease. It can be administered orally or via injection. For Crohn's disease, methotrexate is often used alongside other medications to maintain remission and prevent relapse, particularly after an initial treatment with corticosteroids. However, regular monitoring is necessary due to potential side effects, such as liver and lung damage, increased risk of infection, and severe skin reactions. Folic acid supplements should be avoided as they can reduce methotrexate's effectiveness, while folinic acid (leucovorin) can be used to mitigate side effects. Methotrexate is a key component in the management of Crohn's disease, especially when other treatments are insufficient.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>Methotrexate</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Methotrexate</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Methotrexate</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Based on the provided articles, here are some key points related to the treatment of various diseases:
+1. **Crohn's Disease**: Treatment options for Crohn's disease include corticosteroids, methotrexate, and thiopurines to manage symptoms and prevent relapse. Surgery may be necessary in some cases.
+2. **Psoriasis**: Systemic therapies for psoriasis include non-biologic agents like methotrexate, ciclosporin, and hydroxycarbamide, as well as biologics like infliximab, adalimumab, and etanercept. Biologics target specific aspects of the immune system contributing to psoriasis.
+3. **Primary Sclerosing Cholangitis (PSC)**: Diagnosis of PSC is based on clinical criteria, including elevated serum alkaline phosphatase, cholangiography, and liver biopsy. Treatment options are limited, and the disease often progresses to cirrhosis and liver failure.
+4. **Methotrexate**: Methotrexate is a chemotherapy agent and immune-system suppressant used to treat various cancers, autoimmune diseases, and ectopic pregnancies. Common side effects include nausea, fatigue, and increased risk of infection.
+Some common themes and takeaways from these articles include:
+* **Immune system suppression**: Methotrexate and other systemic therapies for psoriasis and Crohn's disease work by suppressing the immune system.
+* **Limited treatment options**: PSC has limited treatment options, and the disease often progresses to cirrhosis and liver failure.
+* **Side effects**: Methotrexate and other systemic therapies can have significant side effects, including nausea, fatigue, and increased risk of infection.
+* **Biologics**: Biologics like infliximab and etanercept are effective treatments for psoriasis, but their safety during pregnancy and in patients with certain medical conditions is not well established.</t>
         </is>
       </c>
     </row>
@@ -2270,10 +5512,55 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>Hydrocortisone</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Hydrocortisone</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Hydrocortisone</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Hydrocortisone</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Hydrocortisone</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Hydrocortisone</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Hydrocortisone</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
         <is>
           <t>Hydrocortisone</t>
         </is>
@@ -2300,12 +5587,88 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>Tabelecleucel</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tabelecleucel</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tabelecleucel</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>tabelecleucel</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>tabelecleucel</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>tabelecleucel</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>The provided text discusses several Epstein-Barr virus (EBV)-associated lymphoproliferative disorders, each with unique characteristics and clinical implications. Here's a summary of the key points from each section:
+1. **Epstein-Barr Virus-Positive Mucocutaneous Ulcer**:
+   - This is a rare lymphoproliferative disorder characterized by solitary, well-circumscribed ulcers in mucous membranes and skin.
+   - It primarily affects individuals with poor immune function due to conditions like HIV/AIDS, immunosuppressive drug therapy, or allogeneic hematopoietic stem cell transplantation.
+   - The ulcers are caused by EBV-positive B cells and can occur in the oral mucosa, skin, and gastrointestinal tract.
+   - Treatment with rituximab, a monoclonal antibody targeting CD20-positive B cells, has shown excellent responses in persistent or severe cases.
+2. **Epstein-Barr Virus-Related Hemophagocytic Lymphohistiocytosis (HLH)**:
+   - HLH is a rare disorder characterized by systemic inflammation and excessive release of pro-inflammatory cytokines.
+   - It has two types: primary (genetic) and secondary (acquired).
+   - Primary HLH is caused by mutations in genes involved in the cytotoxic function of T and NK cells.
+   - Secondary HLH is associated with malignant and non-malignant diseases that weaken the immune system's ability to control EBV infection.
+   - EBV infection is a common trigger for secondary HLH, particularly in Asian populations.
+3. **EBV-Associated Immunodeficiency-Related Lymphoproliferative Disorders**:
+   - These disorders are heterogeneous and involve EBV-infected B cells, T cells, and/or histiocytic/dendritic cells.
+   - They occur more frequently in individuals with various types of immunodeficiency but can also occur in immunocompetent individuals.
+   - The specific lymphoproliferative disorders are detailed in other sections of the article.
+4. **Epstein-Barr Virus-Positive Plasmablastic Lymphoma (PBL)**:
+   - PBL is an uncommon lymphoma that predominantly affects immune-deficient individuals, especially those with HIV/AIDS.
+   - It can also occur in individuals with organ transplantation, chemotherapy treatment, or age-related immune senescence.
+   - The disease presents as tumors in the head, neck, oral cavity, sinuses, gastrointestinal tract, skin, and other tissues.
+   - Histologically, PBL is classified as monomorphic or plasmacytic, with cells expressing plasma cell markers.
+   - About 70% of PBL cases are EBV-positive, with EBV in latency phase 0 or I.
+   - The prognosis is poor for advanced-stage PBL in HIV-positive patients, but early-stage and EBV-positive patients have better survival rates.
+   - Treatment with CHOP or EPOCH chemotherapy regimens has shown promising results, with EPOCH achieving medium survival rates extending beyond one year.
+These disorders highlight the diverse ways in which EBV can contribute to lymphoproliferative diseases, particularly in immunocompromised individuals.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Tabelecleucel</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>tabelecleucel</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>tabelecleucel</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>The text discusses various types of lymphomas and lymphoproliferative disorders associated with Epstein-Barr virus (EBV) infection. Here are the main points:
+1. **Hodgkin Lymphoma**: The text mentions that Hodgkin lymphoma is a type of lymphoma that can be associated with EBV infection. It is a curable disease, and the five-year survival rate in the US is 89%.
+2. **Non-Hodgkin Lymphomas**: The text also mentions that non-Hodgkin lymphomas are a type of lymphoma that can be associated with EBV infection. The five-year survival rate for non-Hodgkin lymphomas is 74%.
+3. **EBV-Associated Mucocutaneous Ulcer**: This is a rare lymphoproliferative disorder caused by EBV infection, characterized by the formation of ulcers in mucous membranes and skin. It is more common in elderly individuals with poor immune function.
+4. **Hemophagocytic Lymphohistiocytosis (HLH)**: HLH is a rare disorder characterized by a systemic inflammatory condition caused by the proliferation and activation of benign histiocytes, macrophages, and lymphocytes. It is associated with EBV infection in about 33% of cases.
+5. **EBV-Associated Immunodeficiency-Related Lymphoproliferative Disorders**: This category of EBV+ LPD is heterogeneous and involves EBV-infected B cells, T cells, and/or histiocytic/dendritic cells. These LPD occur in individuals with various types of immunodeficiency.
+6. **Plasmablastic Lymphoma (PBL)**: PBL is an uncommon lymphoma that occurs mostly in immune-deficient individuals, primarily those with HIV/AIDS. It is an AIDS-defining clinical condition and is associated with EBV infection in about 70% of cases.
+Overall, the text highlights the association between EBV infection and various types of lymphomas and lymphoproliferative disorders, and emphasizes the importance of considering EBV infection in the diagnosis and treatment of these conditions.</t>
         </is>
       </c>
     </row>
@@ -2338,6 +5701,51 @@
           <t>Nitisinone</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nitisinone</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Nitisinone</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Nitisinone</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Nitisinone</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Nitisinone</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Nitisinone</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Nitisinone</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Nitisinone</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Nitisinone</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2355,15 +5763,60 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>Praziquantel</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Praziquantel</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>praziquantel</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Praziquantel</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Praziquantel</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>praziquantel</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Praziquantel</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Praziquantel</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Praziquantel</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
         <is>
           <t>Praziquantel</t>
         </is>
@@ -2385,15 +5838,60 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Actinomycin D</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Actinomycin D</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Actinomycin D</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>EMA/CO</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Actinomycin D</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Actinomycin D</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Actinomycin D</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Choriocarcinoma</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Actinomycin D</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Actinomycin D</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
         <is>
           <t>Actinomycin D</t>
         </is>
@@ -2428,6 +5926,65 @@
           <t>Temozolomide</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Temozolomide</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Temozolomide</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Temozolomide</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Temozolomide</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>### Summary of Key Points
+**Glioblastoma and Temozolomide:**
+- **Temozolomide** is a chemotherapy drug used to treat glioblastoma, a type of brain cancer. It is indicated for adults with newly diagnosed glioblastoma, often in combination with radiotherapy, and for those with anaplastic astrocytoma that is refractory to standard therapy. In the European Union, it is also used for children and adolescents with malignant gliomas.
+- **Mechanism of Action:** Temozolomide works by alkylating DNA, specifically methylating guanine residues, which damages DNA and leads to cell death. However, some tumors express the MGMT gene, which repairs this damage, reducing the drug's effectiveness.
+- **Pharmacokinetics:** Temozolomide is rapidly absorbed and crosses the blood-brain barrier. It is a prodrug that is converted to its active form, MTIC, which then forms methyldiazonium, the active methylating agent. The drug is primarily excreted through the urine.
+- **Combination Therapies:** Research is exploring the potential of combining temozolomide with other agents like chloroquine, EGCG (from green tea), and O6-benzylguanine to enhance its efficacy. Additionally, efforts are being made to modify the temozolomide molecule itself to improve its activity.
+- **Intranasal Delivery:** Intranasal drug delivery is being investigated as a means to achieve higher drug concentrations in the brain. Early trials have shown promising results, and nanotechnology is being explored to deliver drugs and RNA directly to affected tissue, bypassing the blood-brain barrier.
+- **Enhancer RNAs (eRNAs):** eRNAs are emerging as critical regulators of gene expression in glioblastoma, particularly in modulating oncogenic pathways like the JAK-STAT signaling cascade. For example, silencing TMZR1-eRNA, an eRNA associated with temozolomide resistance, can sensitize tumor cells to temozolomide-induced apoptosis.
+- **Nanoparticle-Based Therapeutics:** Nanoparticles like liposomes, polymeric micelles, and dendrimers are being developed to ferry chemotherapeutics, genes, and immunomodulators across the blood-brain barrier to glioblastoma cells. Preclinical studies show improved tumor drug concentrations and reduced systemic toxicity.
+- **Patient Management:** Cognitive deficits following surgery can be managed with cognitive behavioral therapy, physical exercise, yoga, and meditation. Temozolomide is typically prescribed in cycles, with patients taking the medication once a day for five days, followed by a 28-day break. NHS guidelines recommend limiting the use of temozolomide to six cycles, with continuation beyond 12 cycles being unusual.
+- **Prevention:** There are no known methods to prevent glioblastoma, as it often occurs without prior warning.
+### Conclusion
+Temozolomide remains a critical component in the treatment of glioblastoma, but ongoing research is focused on enhancing its efficacy through combination therapies, novel delivery methods, and targeted molecular modifications. Intranasal delivery and nanoparticle-based therapeutics show promise in improving drug concentrations and overcoming the blood-brain barrier. Additionally, understanding the role of eRNAs and other regulatory molecules may lead to new therapeutic targets. Cognitive rehabilitation strategies are essential for managing post-surgical deficits.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Temozolomide</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Temozolomide</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Temozolomide</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>REASONING: The evidence suggests that temozolomide is the most effective treatment for glioblastoma, especially when combined with radiotherapy. The mechanism of action of temozolomide involves the alkylation of DNA, which triggers the death of tumor cells. However, some tumor cells are resistant to temozolomide due to the expression of the O6-alkylguanine-DNA alkyltransferase (AGT) protein, which is encoded by the MGMT gene. The presence of AGT protein in brain tumors predicts poor response to temozolomide. In contrast, tumors with epigenetic silencing of the MGMT gene are more sensitive to killing by temozolomide.
+CONCLUSION: Based on the evidence, temozolomide is the most effective treatment for glioblastoma, especially when combined with radiotherapy. However, its effectiveness is reduced in tumors with high expression of the MGMT gene. Therefore, the best treatment option for glioblastoma is temozolomide combined with radiotherapy, especially in patients with tumors that have epigenetic silencing of the MGMT gene.
+TREATMENT RECOMMENDATION: Temozolomide combined with radiotherapy is the recommended treatment for glioblastoma, especially in patients with tumors that have epigenetic silencing of the MGMT gene.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2450,10 +6007,55 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>Dabrafenib</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dabrafenib</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dabrafenib</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>dabrafenib</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>dabrafenib</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>dabrafenib</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>dabrafenib</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Dabrafenib</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Dabrafenib</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Dabrafenib</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
         <is>
           <t>Dabrafenib</t>
         </is>
@@ -2475,17 +6077,72 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>Sorafenib</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Atezolizumab and bevacizumab</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Atezolizumab and bevacizumab</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Atezolizumab and bevacizumab</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t>sorafenib</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>sorafenib</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>sorafenib</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Sorafenib is a medication that has been approved for the treatment of advanced renal cell carcinoma and hepatocellular carcinoma (HCC). In the context of HCC, sorafenib has been shown to improve overall survival by 44% compared to placebo, with a median overall survival of 10.7 months in the sorafenib group versus 7.9 months in the placebo group. This improvement led to FDA approval for the treatment of advanced HCC in November 2007.
+However, the cost of sorafenib has been a significant issue, with the UK's National Institute for Clinical Excellence (NICE) declining to approve the drug for use within the NHS in England, Wales, and Northern Ireland due to its high price. In India, a domestic company, Natco Pharma, was granted a license to manufacture generic sorafenib, significantly reducing its cost.
+In terms of treatment options for HCC, radiofrequency ablation (RFA) is a local treatment that uses high-frequency radio waves to destroy tumors by local heating. It is suitable for small tumors (2 cm or less) and has the best outcomes in patients with a solitary tumor less than 4 cm. Other ablation methods, such as cryoablation and percutaneous ethanol injection, may also be used, especially in patients awaiting liver transplantation to lower tumor burden.
+The Barcelona Clinic Liver Cancer (BCLC) staging system is commonly used to guide treatment decisions for HCC. This system takes into account tumor size and number, vascular invasion, extrahepatic spread, liver function, and the patient's general health status and symptoms. The BCLC system is designed to provide a comprehensive assessment of the patient's condition and guide appropriate treatment strategies, including the use of sorafenib for advanced HCC.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>Sorafenib</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Sorafenib</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Sorafenib</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>The text discusses the use of sorafenib in the treatment of various cancers, including renal cell carcinoma and hepatocellular carcinoma (HCC). Sorafenib is a multi-kinase inhibitor that has been shown to prolong progression-free survival in patients with advanced renal cell carcinoma and to improve overall survival in patients with HCC. The text also discusses the use of radiofrequency ablation (RFA) and other ablation methods in the treatment of HCC, including cryoablation, percutaneous ethanol injection, and microwave ablation. The text notes that RFA has been shown to be effective in treating small HCC tumors and can be used in combination with other treatments, such as sorafenib.
+The text also discusses the diagnosis of HCC, including the macroscopic and microscopic appearance of the tumor, and the various staging classification systems available for HCC. The Barcelona Clinic Liver Cancer (BCLC) staging system is discussed as a comprehensive system that takes into account tumor size and number, vascular invasion, extrahepatic spread, liver function, and general health status of the patient.
+Overall, the text provides an overview of the use of sorafenib and other treatments in the management of HCC, as well as the diagnosis and staging of the disease.
+Key points:
+* Sorafenib has been shown to prolong progression-free survival in patients with advanced renal cell carcinoma and to improve overall survival in patients with HCC.
+* RFA has been shown to be effective in treating small HCC tumors and can be used in combination with other treatments, such as sorafenib.
+* The BCLC staging system is a comprehensive system that takes into account tumor size and number, vascular invasion, extrahepatic spread, liver function, and general health status of the patient.
+* The prognosis of HCC is affected by the staging of the tumor, the liver's function due to the effects of chronic liver disease and cirrhosis, and the person's physical performance status.</t>
         </is>
       </c>
     </row>
@@ -2510,12 +6167,89 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>Regorafenib</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Regorafenib</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cabozantinib</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>regorafenib</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>regorafenib</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>regorafenib</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>The information provided covers several aspects of hepatocellular carcinoma (HCC) treatment and research, including drug therapies, clinical trials, and novel approaches. Here's a summary of the key points related to drug therapies and clinical trials for HCC:
+1. **Sorafenib**:
+   - Sorafenib was approved by the FDA in November 2007 for the treatment of hepatocellular carcinoma (HCC).
+   - It is indicated for patients with advanced HCC, increasing survival by approximately 6 months.
+   - In the UK, the National Institute for Clinical Excellence (NICE) initially declined to approve sorafenib due to its high cost, but it is now available in Scotland and other regions.
+2. **Cabozantinib**:
+   - Cabozantinib received FDA approval in January 2019 for the treatment of HCC in patients who have been previously treated with sorafenib.
+   - The approval was based on the Celestial trial (NCT01908426), a randomized, double-blind, placebo-controlled trial.
+   - Cabozantinib is also approved for the treatment of advanced renal cell carcinoma (RCC) and medullary thyroid cancer.
+3. **Selective Internal Radiation Therapy (SIRT)**:
+   - SIRT involves the selective injection of radioisotope agents, typically yttrium-90 (Y-90), into the hepatic artery supplying the tumor.
+   - Products like SIR-Spheres and TheraSphere are used for SIRT, with TheraSphere being FDA-approved for primary liver cancer.
+   - SIRT aims to deliver radiation directly to the tumor while sparing the surrounding liver tissue.
+4. **Emerging Therapies**:
+   - **Mipsagargin (G-202)**: A thapsigargin-based prodrug with cytotoxic activity, currently in phase 2 trials.
+   - **JX-594**: An oncolytic virus with orphan drug designation for HCC, undergoing clinical trials.
+   - **Hepcortespenlisimut-L (Hepko-V5)**: An oral cancer vaccine with orphan drug designation for HCC.
+5. **Research and Biomarkers**:
+   - Research is ongoing to identify genes and proteins that are disregulated in HCC, which could lead to new pharmacological interventions.
+   - Three-dimensional culture methods using patient-derived organoids are being explored for preclinical studies and drug sensitivity testing.
+   - A six-miRNA signature biomarker has been identified to predict HCC recurrence.
+   - Studies are investigating the role of bile acids and gut microbiota in hepatocarcinogenesis.
+These advancements highlight the evolving landscape of HCC treatment, with a focus on targeted therapies, immunotherapies, and personalized medicine approaches.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>Regorafenib</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Regorafenib</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Regorafenib</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Based on the provided text, here are the key points related to the treatment of hepatocellular carcinoma (HCC):
+1. **Transarterial Chemoembolization (TACE)**: TACE is a minimally invasive procedure that involves injecting chemotherapy drugs directly into the liver tumor through the hepatic artery. It has a tumor response rate of approximately 52% and is often used in combination with other treatments.
+2. **Selective Internal Radiation Therapy (SIRT)**: SIRT involves injecting radioactive microspheres into the hepatic artery to deliver radiation directly to the tumor. It has similar efficacy to TACE and is used to treat HCC.
+3. **Sorafenib**: Sorafenib is a targeted therapy that has been approved for the treatment of HCC. It has been shown to increase survival in patients with HCC, but its high cost has been a limitation in some countries.
+4. **Cabozantinib**: Cabozantinib is a targeted therapy that has been approved for the treatment of HCC. It has been shown to improve survival in patients with HCC and is used as a second-line treatment.
+5. **Liver Transplantation**: Liver transplantation is a curative treatment option for HCC, but it is limited by the availability of donor organs.
+6. **Biomarkers**: Researchers are exploring various biomarkers, including miRNAs, to identify patients who are most likely to benefit from treatment.
+7. **Targeted Therapies**: Targeted therapies, such as cabozantinib and sorafenib, are being explored as potential treatments for HCC.
+8. **Oncolytic Viruses**: Oncolytic viruses, such as JX-594, are being investigated as potential treatments for HCC.
+9. **Immunotherapy**: Immunotherapy, such as the use of cancer vaccines, is being explored as a potential treatment for HCC.
+Overall, the treatment of HCC is complex and often involves a combination of treatments. Researchers are continuing to explore new and innovative treatments to improve outcomes for patients with HCC.</t>
         </is>
       </c>
     </row>
@@ -2548,6 +6282,60 @@
           <t>Warfarin</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Based on the information provided, the use of direct oral anticoagulants (DOACs) such as dabigatran, rivaroxaban, edoxaban, and apixaban in people with cancer who develop pulmonary embolism (PE) or deep vein thrombosis (DVT) is a topic of interest. However, the standard anticoagulation therapy for these conditions in people with cancer is typically low molecular weight heparin (LMWH) due to its favorable safety profile and lack of teratogenic effects, especially in pregnant women. 
+For people with cancer who develop PE or DVT, LMWH is usually the preferred initial treatment. However, in some cases, DOACs might be considered as an alternative, particularly for long-term management after the initial LMWH therapy. The decision to use DOACs instead of warfarin or LMWH should be based on the patient's specific clinical situation, including the presence of cancer, the risk of bleeding, and the need for rapid reversal of anticoagulation in case of emergency surgery or bleeding complications.
+The duration of anticoagulation therapy is typically 3 to 6 months, but it can be extended to lifelong anticoagulation if there are no transient risk factors or if there have been previous DVTs or PEs. For patients with cancer, the duration of anticoagulation may be longer due to the ongoing risk of thromboembolic events.
+In summary, while DOACs are effective alternatives to warfarin for anticoagulation, LMWH remains the preferred initial treatment for people with cancer who develop PE or DVT. The choice between LMWH and DOACs should be individualized based on the patient's clinical profile and the need for rapid anticoagulation reversal.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Warfarin</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Based on the provided text, here are some key points related to the use of warfarin and other anticoagulants:
+1.  **Warfarin vs. other anticoagulants**: Warfarin is often used for the prevention and treatment of venous thrombosis, pulmonary embolism, and thromboembolic complications associated with atrial fibrillation and/or cardiac valve replacement. However, newer anticoagulants such as dabigatran, apixaban, edoxaban, and rivaroxaban have been approved for these uses and may offer benefits such as reduced need for monitoring.
+2.  **Monitoring and dosing**: Warfarin requires close monitoring of the degree of anticoagulation using an INR test. The frequency of monitoring depends on the patient's condition and the stability of their INR levels.
+3.  **Side effects and overdose**: The major side effect of warfarin use is bleeding, which can be increased by interactions with other medications or foods. In cases of overdose, the effects of warfarin can be reversed with vitamin K, prothrombin complex concentrate (PCC), or fresh frozen plasma (FFP).
+4.  **Classification of atrial fibrillation**: Atrial fibrillation can be classified into different categories based on the duration and frequency of episodes, including paroxysmal, persistent, and long-standing persistent AF.
+5.  **Screening for atrial fibrillation**: Guidelines recommend opportunistic screening for atrial fibrillation in those 65 years and older, as it is often asymptomatic and can be detected using single-timepoint screening.
+These points highlight the importance of careful monitoring and management of anticoagulation therapy, as well as the need for accurate classification and screening of atrial fibrillation.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2565,15 +6353,60 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Betaxolol</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Betaxolol</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Betaxolol</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>levobunolol</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Betaxolol</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Betaxolol</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Betaxolol</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Timolol</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Betaxolol</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Betaxolol</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
         <is>
           <t>Betaxolol</t>
         </is>
@@ -2595,15 +6428,56 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>CGRP inhibitors</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Topiramate</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
         <is>
           <t>Propranolol</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Propranolol - No</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
         <is>
           <t>Propranolol</t>
         </is>
@@ -2625,17 +6499,70 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>Acetaminophen</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Acetaminophen</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Acetaminophen</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>acetaminophen</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>acetaminophen</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>Ibuprofen</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Paracetamol (acetaminophen) is not considered a nonsteroidal anti-inflammatory drug (NSAID) because it has little anti-inflammatory activity. However, it does play a role in pain relief, primarily by blocking cyclooxygenase-2 (COX-2) activity, mainly in the central nervous system. This mechanism is different from NSAIDs, which inhibit both COX-1 and COX-2 enzymes, leading to potential gastrointestinal side effects such as diarrhea, vomiting, and abdominal pain. Paracetamol is generally well-tolerated with fewer side effects compared to NSAIDs, making it a preferred choice for pain relief and fever reduction in many cases.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Acetaminophen</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t>Misoprostol</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Misoprostol</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Based on the provided articles, here are the key points related to the comparison of paracetamol and ibuprofen:
+1.  **Tolerability**: Paracetamol is well-tolerated with fewer side effects compared to ibuprofen, which can cause diarrhea, vomiting, and abdominal pain.
+2.  **Gastric Irritation**: Paracetamol does not cause gastric irritation, unlike ibuprofen, which can lead to stomach ulcers and internal bleeding.
+3.  **Mechanism of Action**: Both paracetamol and ibuprofen inhibit the cyclooxygenase (COX) enzymes, but paracetamol has a more complex mechanism of action, involving the inhibition of COX-2 in the central nervous system and COX-1 in the periphery.
+4.  **Pain Relief**: Both medications are effective for mild to moderate pain, but paracetamol may be more effective for acute pain, while ibuprofen may be more effective for chronic pain.
+5.  **Fever Reduction**: Paracetamol is effective for reducing fever, but its benefits are unclear, and it may not be as effective as ibuprofen for this purpose.
+6.  **Antipyretic Properties**: Paracetamol's antipyretic properties are not well understood, and its use for fever reduction in adults is not supported by high-quality evidence.
+7.  **Interactions**: Both medications interact with the endocannabinoid system, but the mechanisms of these interactions are not fully understood.
+In summary, paracetamol and ibuprofen have different mechanisms of action, tolerability profiles, and uses. While paracetamol is generally well-tolerated and effective for mild to moderate pain and fever reduction, ibuprofen may be more effective for chronic pain and has a broader range of indications.</t>
         </is>
       </c>
     </row>
@@ -2655,17 +6582,91 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>Lamotrigine</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Lamotrigine</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Lamotrigine</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Lamotrigine</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Lamotrigine</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Lamotrigine</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>The information provided about amitriptyline and its use in treating depression, particularly in the context of bipolar disorder and schizophrenia, highlights several important considerations:
+1. **Pupil Dilation and Psychosis**: Amitriptyline can cause dilation of the pupils, which may exacerbate psychotic symptoms in individuals with schizophrenia. Therefore, it should be used cautiously in patients with a history of psychosis.
+2. **Switch to Mania**: In patients with bipolar disorder, amitriptyline can potentially trigger a switch from depression to mania or hypomania. This is a critical consideration when prescribing the medication to individuals with a history of bipolar disorder.
+3. **CYP2D6 Metabolism**: Patients who are poor metabolizers of CYP2D6 enzymes should avoid amitriptyline due to the risk of increased side effects. If its use is necessary, a reduced dose is recommended to mitigate these risks.
+4. **Pregnancy and Lactation**: Amitriptyline can be used during pregnancy and lactation, especially when selective serotonin reuptake inhibitors (SSRIs) have been ineffective. However, careful monitoring and consideration of potential risks are essential.
+In the context of bipolar disorder, it is crucial to differentiate between bipolar disorder and other conditions that may present similarly, such as major depressive disorder, ADHD, PTSD, and borderline personality disorder. The nature of mood swings in bipolar disorder involves sustained changes over days to weeks, whereas those in borderline personality disorder are often sudden and short-lived.
+### Diagnosis and Differential Diagnosis
+- **Schizophrenia**: Schizophrenia can mimic bipolar disorder, but the nature of mood swings differs significantly.
+- **Major Depressive Disorder**: Bipolar disorder can be initially misdiagnosed as major depressive disorder, especially during depressive episodes.
+- **ADHD, PTSD, Borderline Personality Disorder**: These conditions can also present with mood swings, but the pattern and duration of symptoms differ from bipolar disorder.
+### Criteria and Subtypes
+- **Bipolar I Disorder**: Requires at least one manic episode.
+- **Bipolar II Disorder**: Involves hypomanic episodes and major depressive episodes, but no full manic episodes.
+- **Cyclothymia**: Characterized by hypomanic and depressive symptoms that do not meet criteria for major depressive episodes.
+### Management
+- **Psychosocial Interventions**: Cognitive behavioral therapy (CBT), family-focused therapy, psychoeducation, and interpersonal and social rhythm therapy are effective.
+- **Medication**: Mood stabilizers and atypical antipsychotics are commonly prescribed. Lithium is approved for children with bipolar disorder.
+- **Treatment-Resistant Bipolar Disorder**: Guidelines for managing treatment-resistant bipolar disorder include evidence-based options and careful monitoring.
+### Summary
+Amitriptyline should be used with caution in patients with bipolar disorder or schizophrenia due to the risk of exacerbating symptoms. Proper diagnosis and differentiation from other conditions are essential for effective management. Psychosocial interventions and appropriate medication are key components of treatment, with careful consideration of individual patient factors such as CYP2D6 metabolism and pregnancy status.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Lamotrigine</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Lamotrigine</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Lamotrigine</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Based on the provided text, here are some key points about bipolar disorder:
+1.  **Hypomanic episodes**: These are milder forms of mania, characterized by at least four days of elevated mood, energy, and activity, but without significant impairment in social or occupational functioning.
+2.  **Depressive episodes**: These are characterized by persistent feelings of sadness, irritability, loss of interest in activities, and other symptoms that can be severe and impair daily functioning.
+3.  **Differential diagnosis**: Bipolar disorder can be misdiagnosed as other conditions, such as schizophrenia, major depressive disorder, ADHD, PTSD, and personality disorders.
+4.  **Subtypes**: Bipolar disorder is classified into three subtypes:
+	*   **Bipolar I disorder**: Characterized by at least one manic episode, with or without depressive episodes.
+	*   **Bipolar II disorder**: Characterized by at least one hypomanic episode and one major depressive episode.
+	*   **Cyclothymic disorder**: Characterized by periods of hypomanic symptoms and depressive symptoms that last at least two years.
+5.  **Treatment**: Treatment for bipolar disorder typically involves a combination of medication and psychotherapy. Medications may include mood stabilizers, atypical antipsychotics, and antidepressants. Psychotherapy may include cognitive behavioral therapy, family-focused therapy, and psychoeducation.
+6.  **Resistance to treatment**: Some individuals with bipolar disorder may not respond to treatment, which can be referred to as treatment-resistant bipolar disorder.
+Overall, bipolar disorder is a complex condition that requires a comprehensive treatment approach, including medication and psychotherapy, to manage symptoms and improve quality of life.</t>
         </is>
       </c>
     </row>
@@ -2685,17 +6686,83 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Atomoxetine</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Atomoxetine</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Atomoxetine</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Strattera</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Atomoxetine</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Atomoxetine</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>The management of ADHD typically involves a combination of medication and psychotherapy, with medication being the most effective treatment. Medications used include stimulants, non-stimulants such as atomoxetine, and alpha-2 adrenergic receptor agonists. These medications can improve long-term outcomes and reduce risks such as obesity, but they also come with some risks of adverse events. Cognitive Behavioral Therapy (CBT) can also be used in conjunction with medication to address problems that persist after medication has been optimized. 
+The genetic basis of ADHD is significant, with heritability estimates ranging from 70-80%. The disorder is polygenic, meaning it arises through the accumulation of many genetic risks each having a very small effect. Several genes are involved, including those affecting dopamine neurotransmission. The siblings of children with ADHD are three to four times more likely to develop the disorder than siblings of children without the disorder. 
+ADHD is characterized by a core deficit in executive functions, such as attentional control, inhibitory control, and working memory. This can lead to difficulties with organization, time management, and maintaining concentration. The disorder may not fully manifest until adolescence or early adulthood due to the increasing demands for executive control as a person gets older. 
+In terms of causation, while ADHD can be caused by genetic factors, it can also be triggered by environmental factors such as prenatal exposure to biohazards or traumatic brain injury. However, the precise causes of ADHD are often unknown in individual cases. 
+Lastly, it's worth noting that while insomnia can be caused by many conditions, it can also occur without any identifiable cause, known as primary insomnia. This can be perpetuated by anxiety or fear caused by the sleeplessness itself. Conditions such as heart disease, restless legs syndrome, and neurological disorders can also cause insomnia. 
+In summary, ADHD is a complex disorder with both genetic and environmental factors contributing to its development. Management typically involves a combination of medication and psychotherapy, while insomnia can be caused by a variety of factors and may persist due to anxiety or fear caused by the condition itself.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Non-stimulant</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Atomoxetine</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Atomoxetine</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>The text discusses various topics related to Attention Deficit Hyperactivity Disorder (ADHD), Insomnia, and their causes, management, and mechanisms.
+**ADHD**
+*   The management of ADHD typically involves counseling or medications, either alone or in combination.
+*   Medications used include stimulants, atomoxetine, alpha-2 adrenergic receptor agonists, and sometimes antidepressants.
+*   The disorder is primarily genetic, with a heritability rate of 70-80%, and environmental risks exert their effects very early in life, in the prenatal or early postnatal period.
+*   The siblings of children with ADHD are three to four times more likely to develop the disorder than siblings of children without the disorder.
+*   A common variant of a gene called latrophilin 3 is estimated to be responsible for about 9% of cases and when this variant is present, people are particularly responsive to stimulant medication.
+**Insomnia**
+*   Insomnia can be caused by many conditions, but it can also occur without any identifiable cause, known as primary insomnia.
+*   Primary insomnia may also have an initial identifiable cause but continues after the cause is no longer present.
+*   Symptoms of insomnia can be caused by or associated with sleep breathing disorders, use of psychoactive drugs, use of or withdrawal from alcohol and other sedatives, heart disease, restless legs syndrome, periodic limb movement disorder, pain, hormone shifts, life events, gastrointestinal issues, mental, neurobehavioral, or neurodevelopmental disorders, disturbances of the circadian rhythm, certain neurological disorders, medical conditions, abuse of over-the-counter or prescription sleep aids, poor sleep hygiene, and a rare genetic condition.
+**Mechanisms**
+*   ADHD arises from a core deficit in executive functions, which are a set of cognitive processes that are required to successfully select and monitor behaviors that facilitate the attainment of one's chosen goals.
+*   People with ADHD appear to have unimpaired long-term memory, and deficits in long-term recall appear to be attributed to impairments in working memory.
+*   ADHD has also been associated with motivational deficits in children.
+*   Children with ADHD often find it difficult to focus on long-term over short-term rewards, and exhibit impulsive behavior for short-term rewards.
+*   Paradoxical reactions to neuroactive substances are common in people with ADHD, and these reactions are often unexpected and opposite to the normal effect.</t>
         </is>
       </c>
     </row>
@@ -2715,17 +6782,109 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>Nitrofurantoin</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Nitrofurantoin</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>Cephalexin</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cephalexin</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t>nitrofurantoin</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>nitrofurantoin</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>nitrofurantoin</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>### Summary of Key Points for Each Article Section
+**Article: Cefalexin**
+- **Summary**: Cefalexin is an antibiotic used to treat bacterial infections, including those of the middle ear, bone and joint, skin, urinary tract, and certain types of pneumonia and strep throat. It is not effective against MRSA, most enterococcus, or pseudomonas. Common side effects include stomach upset and diarrhea. It can be used in those with mild or moderate penicillin allergies but not severe ones. It is safe for use during pregnancy and breastfeeding and can be used in children and the elderly. It was developed in 1967 and is widely available as a generic medication.
+**Article: Amoxicillin**
+- **Summary**: Amoxicillin is an antibiotic used to treat bacterial infections such as middle ear infections, strep throat, pneumonia, skin infections, and urinary tract infections. It is taken orally or by injection. Common side effects include nausea and rash. It should not be used in those allergic to penicillin. Amoxicillin is safe for use during pregnancy and breastfeeding. It was discovered in 1958 and came into medical use in 1972. It is one of the most commonly prescribed antibiotics in children and is available as a generic medication.
+**Article: Urinary Tract Infection (UTI)**
+- **Epidemiology**: UTIs occur more frequently in females than males, with a higher incidence between the ages of 16 and 35 years. Recurrences are common, with nearly half of people getting a second infection within a year. Rates of asymptomatic bacteria in the urine increase with age, especially in elderly women in care homes. UTIs may affect 10% of people during childhood, with uncircumcised males less than three months old and females less than one year old being most at risk.
+- **Diagnosis**: A positive urinary culture is required for diagnosis in children. Different cutoffs are used for different sample collection methods. Imaging studies like renal ultrasound and voiding cystourethrogram are recommended for children under two years old who have had a UTI. Differential diagnosis includes cervicitis, vaginitis, interstitial cystitis, prostatitis, and hemorrhagic cystitis.
+- **Prevention**: For peri-menopausal or postmenopausal women, topical vaginal estrogen can reduce recurrence. Low-dose antibiotics can be used after triggering events. Methenamine is another option for prevention. Continuous antibiotics are recommended for recurrent UTIs. Antibiotics after short-term catheterization decrease the risk of bladder infections. Vaccines are in development. Circumcision of boys can reduce UTI incidence. Cranberry products can reduce UTI risk in certain groups, but evidence for d-mannose is weak. Probiotics might help reduce UTI recurrence.
+### Key Points for Each Section
+**Cefalexin Summary**
+- **Indications**: Treats bacterial infections, including middle ear, bone and joint, skin, urinary tract, pneumonia, and strep throat.
+- **Contraindications**: Not effective against MRSA, most enterococcus, or pseudomonas.
+- **Side Effects**: Stomach upset, diarrhea, allergic reactions, and Clostridioides difficile infections.
+- **Use in Special Populations**: Safe during pregnancy and breastfeeding; can be used in children and the elderly.
+- **Development and Availability**: Developed in 1967, first marketed in 1969, available as a generic medication.
+**Amoxicillin Summary**
+- **Indications**: Treats bacterial infections such as middle ear infections, strep throat, pneumonia, skin infections, and urinary tract infections.
+- **Side Effects**: Nausea, rash, yeast infections, and diarrhea when used with clavulanic acid.
+- **Contraindications**: Not for use in those allergic to penicillin.
+- **Use in Special Populations**: Safe during pregnancy and breastfeeding.
+- **Development and Availability**: Discovered in 1958, came into medical use in 1972, available as a generic medication.
+**UTI Epidemiology**
+- **Incidence**: Higher in females, especially between ages 16 and 35.
+- **Recurrence**: Nearly half of people get a second infection within a year.
+- **Asymptomatic Bacteria**: Higher rates in elderly women in care homes.
+- **Children**: Most common in uncircumcised males under three months and females under one year.
+**UTI Diagnosis**
+- **Children**: Positive urinary culture required, different cutoffs for sample collection methods.
+- **Imaging**: Recommended for children under two years old who have had a UTI.
+- **Differential Diagnosis**: Cervicitis, vaginitis, interstitial cystitis, prostatitis, hemorrhagic cystitis.
+**UTI Prevention**
+- **Women**: Topical vaginal estrogen, low-dose antibiotics after triggering events.
+- **General**: Methenamine, continuous antibiotics for recurrent UTIs.
+- **Catheterization**: Antibiotics after short-term catheterization.
+- **Vaccines**: In development.
+- **Circumcision**: Protective effect in boys.
+- **Dietary Supplements**: Cranberry products, probiotics, d-mannose (limited evidence).
+These summaries provide a comprehensive overview of the key points in each article section, highlighting the important aspects of cefalexin, amoxicillin, and urinary tract infections.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Cephalexin</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t>Nitrofurantoin</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Nitrofurantoin</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>The text discusses various topics related to antibiotics and urinary tract infections (UTIs). Here are some key points:
+1. **Cefalexin**: Cefalexin is a β-lactam antibiotic that belongs to the first-generation cephalosporins class. It is used to treat bacterial infections, including those of the middle ear, bone and joint, skin, and urinary tract. It is not effective against infections caused by methicillin-resistant Staphylococcus aureus (MRSA), most Enterococcus, or Pseudomonas.
+2. **Amoxicillin**: Amoxicillin is an antibiotic medication that belongs to the aminopenicillin class of the penicillin family. It is used to treat bacterial infections, including middle ear infections, strep throat, pneumonia, skin infections, and urinary tract infections.
+3. **Urinary Tract Infections (UTIs)**: UTIs are more common in females than males, and they occur most frequently between the ages of 16 and 35 years. Recurrences are common, with nearly half of people getting a second infection within a year.
+4. **Diagnosis of UTIs in Children**: A positive urinary culture is required to diagnose a UTI in children. Contamination poses a frequent challenge, and a cutoff of 105 cfu/ml is used for a "clean-catch" mid-stream sample.
+5. **Prevention of UTIs**: Topical vaginal estrogen has been found to reduce recurrence in peri-menopausal or postmenopausal women with recurrent infections. A single dose of antibiotics after a triggering event (like intercourse) can be considered for other people. Methenamine is another medication used for prevention.
+6. **UTI Vaccines**: Several UTI vaccines are in development as of 2025.
+7. **Circumcision**: Circumcision of boys has been observed to exhibit a strong protective effect against UTIs, with some research suggesting as much as a 90% reduction in symptomatic UTI incidence among male infants.
+8. **Dietary Supplements**: Cranberry products can reduce the risk of UTIs in certain groups (women with reoccurring UTIs, children, and people having had clinical interventions), but not in pregnant women, the elderly, or people with urination disorders. D-mannose is often marketed as a dietary supplement that prevents UTIs, but there is little evidence supporting its use.
+Overall, the text provides information on various antibiotics and treatments for UTIs, as well as prevention strategies and dietary supplements that may help reduce the risk of UTIs.</t>
         </is>
       </c>
     </row>
@@ -2750,12 +6909,93 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>Lorazepam</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>No specific hypnotic medication is preferred; benzodiazepines are contraindicated.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the articles, here's a summary of the management and treatment options for Chronic Obstructive Pulmonary Disease (COPD):
+### Management and Treatment of COPD
+#### Early Diagnosis and Prevention
+- **Early Detection:** Early diagnosis and intervention are crucial to improve quality of life and reduce flare-ups.
+- **Smoking Cessation:** Stopping smoking can significantly reduce the rate of lung function decline and decrease mortality from smoking-related diseases like lung cancer and cardiovascular disease.
+- **Vaccinations:** Pneumococcal and annual influenza vaccinations are recommended to reduce the risk of flare-ups. As of 2024, the CDC and GOLD also recommend the RSV vaccine for individuals above 60 years.
+- **Covid-19 Vaccination:** Recommended in line with national guidelines.
+#### Non-Pharmacological Interventions
+- **Pulmonary Rehabilitation:** Helps improve exercise capacity and quality of life, especially in early, mild COPD.
+- **Action Plan:** Personalized action plans, education, and support for early treatment of exacerbations can reduce hospital visits.
+#### Medical Treatments
+- **Bronchodilators:** 
+  - **Short-Acting Bronchodilators:** Provide relief for 4-6 hours and are used for symptom relief.
+  - **Long-Acting Bronchodilators:** 
+    - **Long-Acting Beta-2 Agonists (LABAs):** Formoterol, salmeterol, and indacaterol are commonly used. Indacaterol requires once-daily dosing.
+    - **Long-Acting Muscarinic Antagonists (LAMAs):** Tiotropium is a commonly used LAMA.
+  - **Combination Therapy:** Dual bronchodilator therapy (LABA + LAMA) is recommended for more severe symptoms and can reduce COPD exacerbations and improve quality of life compared to long-acting bronchodilators alone.
+- **Inhaled Corticosteroids (ICS):** Used in combination with LABAs for more severe cases, especially in those with high blood eosinophil counts.
+- **Antibiotics:** Used for treating exacerbations.
+- **Non-Invasive Ventilation:** Used to support breathing and reduce daytime breathlessness.
+- **Palliative Care:** Focused on relieving symptoms in end-stage disease, including the use of morphine to improve exercise tolerance.
+#### Management of Exacerbations
+- **Acute Hypercapnic Respiratory Failure:** Bilevel positive airway pressure (BiPAP) is preferred over continuous positive airway pressure (CPAP) in treating cases of cardiogenic pulmonary edema with hypercapnia.
+### Summary of Guidelines
+- **2018 NICE Guidelines:** Recommend dual long-acting bronchodilators as a preferred approach over starting one long-acting bronchodilator and adding another later.
+- **2022 GOLD Report:** Recommends initial monotherapy with LABA or LAMA for most patients, with dual bronchodilator therapy (LABA + LAMA) for more severe symptoms.
+- **2023 GOLD Report:** Suggests LABA or LAMA for patients in Class A, combined LABA + LAMA for those in Group B or E, and LABA + LAMA + ICS for those in Group E with high blood eosinophil counts.
+- **ATS Guidelines:** Strongly recommend LABA + LAMA combination therapy over LABA or LAMA monotherapy in patients with COPD and dyspnea or exercise intolerance.
+By following these guidelines and management strategies, healthcare providers can effectively manage COPD and improve the quality of life for patients.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>Midazolam</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Midazolam</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>The text discusses the management and treatment of Chronic Obstructive Pulmonary Disease (COPD). It highlights the importance of early diagnosis and intervention, as well as the use of various medications and therapies to manage symptoms and slow disease progression. The text also mentions the use of bronchodilators, corticosteroids, and antibiotics to manage exacerbations, as well as the use of non-invasive ventilation to support breathing.
+The text also discusses the use of lorazepam, a benzodiazepine, in the management of COPD. Lorazepam is used to reduce anxiety and agitation, and to induce anterograde amnesia for procedures. It is also used to treat agitation and acute delirium, and to manage symptoms of catatonia.
+The text highlights the importance of individualized treatment plans, and the need for healthcare providers to work with patients to develop personalized action plans and education to manage symptoms and prevent exacerbations.
+The text also mentions the use of dual long-acting bronchodilators, with economic modeling suggesting that this approach is preferable to starting one long-acting bronchodilator and adding another later. The text also mentions the use of inhaled corticosteroids and long-acting beta-2 agonists as initial monotherapy for most patients.
+Overall, the text emphasizes the importance of early diagnosis and intervention, individualized treatment plans, and the use of various medications and therapies to manage symptoms and slow disease progression in COPD.
+The main points of the text are:
+* COPD has no cure, but symptoms can be managed and progression can be slowed
+* Early diagnosis and intervention are key to managing COPD
+* Individualized treatment plans are essential for managing COPD
+* Dual long-acting bronchodilators are recommended as initial monotherapy for most patients
+* Inhaled corticosteroids and long-acting beta-2 agonists are recommended as initial monotherapy for most patients
+* Lorazepam is used to reduce anxiety and agitation, and to induce anterograde amnesia for procedures
+* Lorazepam is used to treat agitation and acute delirium, and to manage symptoms of catatonia.</t>
         </is>
       </c>
     </row>
@@ -2780,10 +7020,55 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Cholestyramine</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
           <t>cholestyramine</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>cholestyramine</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>cholestyramine</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Fibrates</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Labetalol</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2806,12 +7091,68 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>Amisulpride</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Amisulpride</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ziprasidone</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>amisulpride</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>amisulpride</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
           <t>risperidone</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Based on the provided information, it appears that the medication Cobenfy (xanomeline/trospium chloride) has been approved for use and has shown promise in improving symptoms of schizophrenia. However, the article excerpt provided does not directly discuss Cobenfy or its effects. Instead, it focuses on ziprasidone, a second-generation antipsychotic, and its adverse effects, discontinuation symptoms, and risk factors associated with other medications.
+To address the question about Cobenfy and its potential benefits, we can summarize the relevant information as follows:
+1. **Cobenfy (Xanomeline/Trospium Chloride)**: This fixed-dose combination medication has been approved and has shown efficacy in improving symptoms of schizophrenia according to a 2025 meta-analysis. Xanomeline is a muscarinic receptor agonist, and trospium chloride is an anticholinergic agent. The combination aims to enhance cognitive function and reduce negative symptoms of schizophrenia.
+2. **Discontinuation of Antipsychotics**: The British National Formulary recommends a gradual withdrawal of antipsychotics to avoid acute withdrawal syndrome or rapid relapse. Symptoms of withdrawal can include nausea, vomiting, loss of appetite, restlessness, increased sweating, and trouble sleeping. There is also tentative evidence that discontinuation can result in psychosis or reoccurrence of the treated condition.
+3. **Drug-Induced Obesity**: Certain medications, including atypical antipsychotics, can cause weight gain or changes in body composition. Ziprasidone, while having a lower risk of weight gain compared to other atypical antipsychotics, still has the potential to cause weight gain. Other medications like insulin, sulfonylureas, thiazolidinediones, and some anticonvulsants can also contribute to obesity.
+4. **Osteoporosis Risk Factors**: Certain medications, such as glucocorticosteroids and anticonvulsants, can increase the risk of osteoporosis. Long-term use of proton pump inhibitors and thiazolidinediones (used for diabetes) can also contribute to bone density loss.
+In summary, while Cobenfy shows promise in treating schizophrenia, it is important to consider the potential side effects and risks associated with antipsychotic medications, including weight gain and osteoporosis. Gradual discontinuation of antipsychotics is recommended to avoid withdrawal symptoms and potential relapse.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Haloperidol</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Clozapine</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>amisulpride</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>The articles discuss various topics related to antipsychotic medications, including their use in treating schizophrenia, potential side effects, and interactions with other medications.
+The article on Ziprasidone mentions that it is a second-generation antipsychotic (SGA) that received a boxed warning in the US due to increased mortality in elderly people with dementia-related psychosis. Common adverse effects of Ziprasidone include sleepiness, headache, dry mouth, and extrapyramidal symptoms.
+The article on Obesity mentions that certain medications, including antipsychotics, can increase the risk of obesity. It also notes that obesity is not regarded as a psychiatric disorder, but rather a physical condition that can be influenced by various factors, including medication use.
+The article on Osteoporosis discusses the risk factors for osteoporosis, including medication use. It notes that certain medications, such as glucocorticosteroids and anticonvulsants, can increase the risk of osteoporosis.
+The article on Schizophrenia provides a historical context for the diagnosis and treatment of schizophrenia. It notes that the diagnosis of schizophrenia has been broad and clinically based in the past, and that the diagnostic model has shifted over time to focus on an evidence-based medical model.
+Overall, the articles highlight the importance of considering the potential side effects and interactions of antipsychotic medications, as well as the need for a nuanced understanding of the diagnosis and treatment of schizophrenia.</t>
         </is>
       </c>
     </row>
@@ -2831,17 +7172,62 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>Calcitriol</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Insufficient evidence</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Calcitriol</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Calcitriol</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>Sevelamer</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Calcitriol</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Dapagliflozin</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Bisphosphonates</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>Sevelamer</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Dapagliflozin</t>
         </is>
       </c>
     </row>
@@ -2874,6 +7260,57 @@
           <t>Bupropion</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Based on the information provided, varenicline at a dose of 1 mg/day leads to an abstinence rate of 25%, while the higher dose of varenicline (presumably 2 mg/day) leads to a higher abstinence rate of 33.2%. This indicates that the higher dose of varenicline is more effective for smoking cessation compared to the lower dose. Additionally, varenicline is noted to be more effective than bupropion for maintaining smoking abstinence, as bupropion's effectiveness declines over time from 37% at three months to 20% at one year. Combining bupropion and nicotine replacement therapy does not improve the quitting rate, further emphasizing the superior efficacy of varenicline for smoking cessation at the higher dose.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Based on the provided text, here are the key points related to the effectiveness of bupropion for smoking cessation and major depressive disorder:
+1.  **Smoking Cessation**: Bupropion is effective for smoking cessation, with a 1.6-fold increase in the likelihood of quitting compared to placebo. It is as effective as nicotine replacement therapy but inferior to varenicline.
+2.  **Major Depressive Disorder**: Bupropion is effective for major depressive disorder, with a 50-75% response rate to the first antidepressant administered. It may be used as an adjunctive treatment to augment the effects of other antidepressants.
+3.  **Antidepressant Medication**: Antidepressant medication treatment is usually continued for six to nine months after remission to minimize the chance of recurrence. SSRI's are the primary medications prescribed due to their relatively mild side effects and safety.
+4.  **Lifestyle Changes**: Physical exercise, sleep, and diet may also play a role in depression, and interventions in these areas may be an effective add-on to conventional methods.
+5.  **Side Effects**: Bupropion may increase the risk of psychiatric side effects, including anxiety and insomnia, and may be associated with induction of compulsive behavior. It may also cause antidepressant discontinuation syndrome when abruptly discontinued.
+Overall, bupropion is a useful medication for smoking cessation and major depressive disorder, but it may have side effects and should be used with caution, especially in children and adolescents.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2904,6 +7341,51 @@
           <t>Tamsulosin</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tamsulosin</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Tamsulosin</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>tamsulosin</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Tamsulosin</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>tamsulosin</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Tamsulosin</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Tamsulosin</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Tamsulosin</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Tamsulosin</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2934,6 +7416,64 @@
           <t>Clopidogrel</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Clopidogrel</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>clopidogrel</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Clopidogrel</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Clopidogrel</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the articles, there are several key points to consider regarding the adverse effects and interactions of warfarin, nonsteroidal anti-inflammatory drugs (NSAIDs), and stroke prevention:
+1. **Warfarin Bleeding Risk**: Warfarin's primary adverse effect is bleeding, with a typical yearly rate of 1-3%. The risk of severe bleeding increases significantly when the International Normalized Ratio (INR) exceeds 4.5. Risk factors for bleeding include uncontrolled high blood pressure, abnormal kidney function, previous stroke, previous bleeding condition, labile INR, age over 65, and use of drugs associated with bleeding (e.g., aspirin, NSAIDs).
+2. **Warfarin Necrosis**: This rare but serious complication occurs more frequently in patients with a deficiency of protein C, leading to massive thrombosis, skin necrosis, and gangrene of limbs. It can be mitigated by administering heparin in parallel with warfarin during the initial treatment period.
+3. **NSAID Cardiovascular Risk**: NSAIDs, except for low-dose aspirin, increase the risk of myocardial infarction and stroke, particularly within a week of use. They also increase the risk of heart failure and mortality in people with heart failure. Naproxen may be the least harmful among NSAIDs in terms of cardiovascular risk.
+4. **NSAID and Warfarin Interaction**: Combining warfarin with NSAIDs increases the risk of bleeding. This interaction is a significant concern, especially in patients already at risk due to warfarin therapy.
+5. **Stroke Prevention**: Chronic uncontrolled hypertension and atrial fibrillation are the most important modifiable risk factors for stroke. Other risk factors include high blood cholesterol levels, diabetes, smoking, heavy alcohol use, drug use, and unhealthy diet. NSAID use can increase the risk of ischemic stroke and hemorrhagic stroke via multiple mechanisms.
+6. **Specific Recommendations for Women**: Women with a history of pregnancy complications, such as hypertensive disorders of pregnancy, preterm birth, or small-for-gestational-age infants, face a higher risk of ischemic stroke. Specific recommendations include taking aspirin after the 11th week of pregnancy if there is a history of previous chronic high blood pressure and taking blood pressure medications during pregnancy if the blood pressure is greater than 150 mmHg systolic or 100 mmHg diastolic.
+7. **Erectile Dysfunction Risk**: Long-term use of NSAIDs may be associated with an increased risk of erectile dysfunction, although the evidence is observational and not definitive.
+In summary, the use of warfarin and NSAIDs requires careful management to minimize the risk of bleeding and cardiovascular events. Patients should be closely monitored, and risk factors should be managed aggressively to prevent stroke and other adverse outcomes.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Clopidogrel</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Clopidogrel</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Clopidogrel</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Warfarin is a medication used to prevent blood clots and reduce the risk of stroke, heart attack, and other cardiovascular events. It is commonly used to treat conditions such as atrial fibrillation, deep vein thrombosis, and pulmonary embolism. However, it can have serious side effects, including bleeding, which is the most common and potentially life-threatening complication. The risk of bleeding is increased in people with certain medical conditions, such as kidney disease, and when warfarin is combined with other medications, such as antiplatelet drugs.
+In addition to bleeding, warfarin can also cause other side effects, including skin necrosis, which is a rare but serious complication that occurs when the medication causes the blood to clot too quickly. This can lead to gangrene and amputation of limbs.
+Warfarin is not suitable for everyone, particularly those with a history of bleeding disorders or those taking other medications that increase the risk of bleeding. It is also not recommended for people with certain medical conditions, such as kidney disease or liver disease.
+In terms of prevention, lifestyle factors such as diet, exercise, smoking, and alcohol use can all contribute to the risk of stroke. High blood pressure, high cholesterol, and diabetes are also major risk factors for stroke. Medications such as aspirin and anticoagulants like warfarin can be used to prevent stroke, but they also carry risks, including bleeding.
+Nonsteroidal anti-inflammatory drugs (NSAIDs) can also increase the risk of stroke, particularly when used in combination with other medications. They can also cause other side effects, including gastrointestinal bleeding and kidney damage.
+Overall, warfarin and other medications used to prevent stroke carry risks and benefits that must be carefully weighed by healthcare providers and patients. Lifestyle factors and other medical conditions also play a significant role in the risk of stroke, and addressing these factors can help reduce the risk of stroke and other cardiovascular events.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2956,12 +7496,57 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>TNF inhibitors</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>TNF inhibitors</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>TNF inhibitors</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>TNF_inhibitor</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>TNF_inhibitor</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>TNF_inhibitor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>TNF_inhibitor</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>TNF inhibitors</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t>TNF inhibitor</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>TNF inhibitor</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
         </is>
       </c>
     </row>
@@ -2981,15 +7566,60 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>Allopurinol</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Allopurinol</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Allopurinol</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t>allopurinol</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>allopurinol</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>allopurinol</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>allopurinol</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Colchicine</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Allopurinol</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Allopurinol</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
         <is>
           <t>Allopurinol</t>
         </is>
@@ -3011,17 +7641,92 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t>Leucovorin</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>Folic acid</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Folic acid</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Folic acid</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>leucovorin</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>leucovorin</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>leucovorin</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Based on the provided information, Methotrexate, a commonly used Disease-Modifying Antirheumatic Drug (DMARD) for treating Rheumatoid Arthritis (RA), has several adverse effects that need to be carefully monitored. The most common adverse effects include hepatotoxicity, stomatitis, blood abnormalities such as leukopenia, anemia, and thrombocytopenia, increased risk of infection, hair loss, nausea, reduced appetite, abdominal pain, diarrhea, fatigue, fever, dizziness, drowsiness, headache, acute pneumonitis, and renal impairment. Methotrexate can also cause mucositis and may be associated with a lower incidence of interstitial lung disease (ILD) over time in the context of RA.
+Methotrexate is teratogenic, and it is advised to stop taking it at least four weeks before becoming pregnant and it should be avoided during pregnancy (Pregnancy Category X) and while breastfeeding. However, guidelines have been updated to state that it is safe for a male partner to take methotrexate at any point while trying to conceive.
+Central nervous system reactions to methotrexate have been reported, especially when given via the intrathecal route, which include myelopathies and leukoencephalopathies. Methotrexate also has a variety of cutaneous side effects, particularly when administered in high doses. Another serious possible adverse effect of methotrexate is neurological damage and memory loss, which may result from the drug crossing the blood-brain barrier and damaging neurons in the cerebral cortex. People with cancer who receive the medication often nickname these effects "chemo brain" or "chemo fog."
+In terms of drug interactions, methotrexate can interact with amoxicillin, anticoagulants (dabigatran, warfarin), typhoid, cholera, and BCG vaccines, probenecid, oral contraceptives, allopurinol, mycophenolate (when given intravenously or intramuscularly), aminoglycosides, ciprofloxacin, infusions containing dextran or bicarbonate, and other medications. These interactions can affect the efficacy and safety of methotrexate and other drugs.
+When considering the use of methotrexate in combination with other DMARDs, such as hydroxychloroquine and sulfasalazine, it is important to monitor for potential side effects and drug interactions. Methotrexate is often used in combination with biologics, which can improve ACR50, HAQ scores, and RA remission rates. However, people may experience greater side effects when agents are used in combination.
+In summary, while methotrexate is a highly effective DMARD for treating RA, it is essential to monitor patients closely for adverse effects and drug interactions to ensure safe and effective treatment. Regular monitoring of blood counts, liver function, and renal function is recommended, and patients should be advised to report any new or worsening symptoms promptly.</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>Folinic acid</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Folinic acid</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Folinic acid</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Based on the provided text, the following information can be extracted:
+1.  **Hydroxychloroquine**: 
+    - Half-life: 5 days (previously thought to be 40-50 days)
+    - Tissue uptake is responsible for its long half-life
+    - Steady-state concentrations may take 3-4 months to attain
+    - Combination with methotrexate and biologics improves ACR50, HAQ scores, and RA remission rates
+2.  **Methotrexate**:
+    - Common adverse effects: hepatotoxicity, stomatitis, blood abnormalities, increased risk of infection, hair loss, nausea, reduced appetite, abdominal pain, diarrhea, fatigue, fever, dizziness, drowsiness, headache, acute pneumonitis, and renal impairment
+    - Teratogenic and should be avoided during pregnancy (pregnancy category X)
+    - Neurological damage and memory loss are possible adverse effects
+3.  **Amoxicillin**:
+    - Interactions: anticoagulants (dabigatran, warfarin), methotrexate, typhoid, cholera, and BCG vaccines, probenecid, oral contraceptives, allopurinol, mycophenolate, aminoglycoside, ciprofloxacin, dextran, and bicarbonate
+    - Should not be mixed with blood products, proteinaceous fluids, or intravenous lipid emulsions
+4.  **Crohn's Disease**:
+    - Symptoms: abdominal pain, diarrhea, fever, abdominal distension, and weight loss
+    - Complications: anemia, skin rashes, arthritis, inflammation of the eye, and fatigue
+    - Risk of colorectal cancer and small bowel cancer is increased
+    - Genetics play a significant role, with more than 70 genes involved
+    - Smoking increases the risk of developing Crohn's disease
+    - Treatment options include corticosteroids, methotrexate, thiopurines, and surgery
+5.  **Nonsteroidal Anti-Inflammatory Drugs (NSAIDs)**:
+    - Contraindications: persons over 50 with a family history of gastrointestinal problems, and those with previous gastrointestinal problems from NSAID use
+6.  **Primidone**:
+    - Adverse effects: drowsiness, listlessness, ataxia, visual disturbances, nystagmus, headache, and dizziness
+    - Dupuytren's contracture is a possible side effect, especially in Caucasians
+    - Cardiovascular effects include shortening the QT interval and elevating serum levels of homocysteine and high-density lipoprotein cholesterol</t>
         </is>
       </c>
     </row>
@@ -3041,15 +7746,60 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>Bupropion</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Bupropion</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Carbamazepine</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>bupropion</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Varenicline</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Bupropion</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
         <is>
           <t>Bupropion</t>
         </is>
@@ -3071,15 +7821,56 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Fexofenadine</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Fexofenadine</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Fexofenadine</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
         <is>
           <t>loratadine</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>loratadine</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>loratadine</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Loratadine</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Loratadine</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
         <is>
           <t>Loratadine</t>
         </is>
@@ -3101,17 +7892,76 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t>Pregabalin</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>Duloxetine</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Duloxetine</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Duloxetine</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t>amitriptyline</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>amitriptyline</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>amitriptyline</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>The provided text discusses various aspects of diabetic neuropathy, including diagnosis, treatment, and cranial neuropathy. Here's a summary of the key points:
+### Diagnosis
+Diabetic peripheral neuropathy is diagnosed through a combination of history and physical examination. Common symptoms include pain, numbness, muscle weakness, balance loss, and lower limb dysfunction. Physical examination may reveal changes in foot appearance, ulceration, and diminished ankle reflexes. Useful diagnostic tests include vibration perception testing with a 128-Hz tuning fork and pressure sensation testing with a 5.07 Semmes-Weinstein monofilament. Nerve conduction studies are less commonly used due to their limited correlation with the severity of diabetic neuropathy.
+### Treatment
+Treatment options for diabetic neuropathy include physical therapy, which can help reduce dependency on pain medications and improve symptoms such as deep pain, tingling, muscle cramps, and sexual dysfunction. Techniques like gait training, posture training, and off-loading techniques (e.g., using mobility aids) can prevent and stabilize foot complications. Exercise programs, including stretching and strengthening exercises, can maintain muscle strength and reduce muscle wasting. Heat, therapeutic ultrasound, and hot wax are also beneficial. For sexual dysfunction, pelvic floor muscle exercises can be effective. Electric stimulation of the foot can improve balance and sensation. In some cases, surgery may be considered for nerve decompression to treat diabetic peripheral neuropathy (DPN) with nerve compression, potentially reversing symptoms and preventing complications like ulcers and amputations.
+### Cranial Neuropathy
+Cranial neuropathy in diabetes often affects the oculomotor nerve (CN III), leading to symptoms such as double vision and frontal or orbital pain. The onset is usually abrupt, and the pupil size is typically well-preserved early on due to the peripheral location of parasympathetic nerve fibers. The abducens nerve (CN VI) is also commonly affected, while the trochlear nerve (CN IV) involvement is less common. Diabetics have a higher incidence of entrapment neuropathies, such as carpal tunnel syndrome.
+### Additional Considerations
+Diabetic neuropathy can also cause painful syndromes that mimic other conditions, such as heart attacks, gallbladder inflammation, or appendicitis, due to damage to thoracic or lumbar spinal nerves. Proper diagnosis and management are crucial to prevent complications and improve quality of life for patients with diabetic neuropathy.</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>Amitriptyline</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Amitriptyline</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Amitriptyline</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>The provided text discusses various aspects of diabetic neuropathy, including its diagnosis, treatment, and management of related conditions. Here are the main points:
+1. **Diagnosis**: Diabetic neuropathy can be diagnosed with a history and physical examination. The most useful physical examination findings are an abnormally decreased vibration perception to a 128-hz tuning fork or pressure sensation with a 5.07 Semmes-Weinstein monofilament.
+2. **Treatment**: Treatment options include physical therapy, which can help reduce dependency on pain relieving drug therapies. Physical therapy techniques can alleviate symptoms such as deep pain in the feet and legs, tingling or burning sensation in extremities, muscle cramps, muscle weakness, and sexual dysfunction.
+3. **Cranial Neuropathy**: Cranial nerves can be affected, with oculomotor nerve (cranial nerve #3 or CNIII) being the most common. The onset of a diabetic third nerve palsy is usually abrupt, beginning with frontal or pain around the eye and then double vision.
+4. **Management of Related Conditions**: Beta blockers can exacerbate hypoglycemia by interfering with glycogenolysis and masking signs of hypoglycemia. Abrupt withdrawal of beta blockers can result in a thyroid storm. Bradycardia or AV block can occur unless a pacemaker is present.
+5. **Surgery**: Diabetic peripheral neuropathy (DPN) with superimposed nerve compression may be treatable with multiple nerve decompressions. This procedure can reverse some symptoms and provide protection against serious foot complications.
+Overall, the text highlights the importance of early diagnosis and treatment of diabetic neuropathy to prevent complications and improve quality of life.</t>
         </is>
       </c>
     </row>
@@ -3131,13 +7981,76 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>Benzodiazepines</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>Antidepressant</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Antidepressants</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>SSRIs</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Based on the information provided, benzodiazepines (BZDs) have a complex history and role in treating various conditions, including anxiety and insomnia. Here are key points regarding their use, especially in the context of elderly patients:
+1. **History and Development**: Benzodiazepines were first synthesized in 1955 by Leo Sternbach. Chlordiazepoxide (Liberium) was the first benzodiazepine to be introduced in 1960, followed by diazepam (Valium) in 1963. These drugs quickly replaced barbiturates due to their perceived safety and efficacy.
+2. **Use in Insomnia**: BZDs can be effective for short-term treatment of insomnia, but their use beyond 2 to 4 weeks is discouraged due to the risk of dependence. They improve sleep onset latency and total sleep time but worsen sleep quality by increasing light sleep and decreasing deep sleep. Long-acting BZDs like nitrazepam and diazepam are generally not recommended for insomnia due to residual effects.
+3. **Efficacy and Safety Concerns**: While BZDs are effective for treating anxiety and insomnia, they carry risks such as dependence, tolerance, and withdrawal symptoms. Nonbenzodiazepine hypnotics (Z-drugs) have gained popularity since the 1990s, but their efficacy and safety are comparable to short-acting BZDs. Some experts recommend using nonbenzodiazepines preferentially, but the UK National Institute for Health and Clinical Excellence (NICE) found no convincing evidence favoring Z-drugs over BZDs.
+4. **Use in the Elderly**: BZDs are listed as potentially inappropriate medications for older adults by the American Geriatrics Society. Elderly patients are at increased risk of dependence and adverse effects such as memory problems, daytime sedation, impaired motor coordination, and an increased risk of falls and fractures. Long-term use is associated with cognitive impairment and dementia. Short-acting BZDs like oxazepam and temazepam are preferred over long-acting ones like alprazolam and triazolam in the elderly.
+5. **Alternatives**: Nonbenzodiazepine hypnotics and low doses of sedating antidepressants are sometimes used as alternatives to BZDs in the elderly. Cognitive impairing effects of BZDs can worsen dementia symptoms in elderly patients.
+6. **Dependence and Withdrawal**: BZDs have a high risk of dependence and withdrawal symptoms, which can be severe and long-lasting. Gradual tapering is recommended for withdrawal, with success rates similar in elderly and younger patients.
+7. **Legal and Ethical Considerations**: The introduction of BZDs led to significant legal challenges, including class-action lawsuits in the UK, highlighting concerns about dependence and withdrawal risks that were not adequately communicated to healthcare providers and patients.
+In summary, while BZDs can be effective for short-term use in treating anxiety and insomnia, their long-term use, especially in the elderly, carries significant risks. Alternatives and careful management of BZD use are recommended to minimize adverse effects and dependence.</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Midazolam</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Lorazepam</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>The text discusses the use of benzodiazepines in treating anxiety disorders, insomnia, and other conditions. It highlights the benefits and risks of benzodiazepines, including their effectiveness in reducing anxiety and improving sleep, but also their potential for dependence and withdrawal symptoms. The text also notes that benzodiazepines are not recommended for long-term use, especially in the elderly, due to increased risk of adverse effects such as memory problems, daytime sedation, and increased risk of motor vehicle accidents and falls.
+The text also discusses the use of benzodiazepines in treating insomnia, noting that they can improve sleep-related problems but worsen sleep quality. It also notes that benzodiazepines have a unique history, being responsible for the largest-ever class-action lawsuit against drug manufacturers in the UK.
+In terms of the elderly, the text notes that benzodiazepines have reduced benefits and increased risks, and are listed as a potentially inappropriate medication for older adults by the American Geriatrics Society. It also notes that the benefits of withdrawal include improved cognition, alertness, mobility, reduced risk of incontinence, and a reduced risk of falls and fractures.
+Overall, the text provides a comprehensive overview of the use of benzodiazepines in treating various conditions, highlighting their benefits and risks, and emphasizing the importance of caution and careful consideration when prescribing them, especially in the elderly.
+The main points of the text are:
+* Benzodiazepines are effective in reducing anxiety and improving sleep, but have a potential for dependence and withdrawal symptoms.
+* Benzodiazepines are not recommended for long-term use, especially in the elderly, due to increased risk of adverse effects.
+* Benzodiazepines have a unique history, being responsible for the largest-ever class-action lawsuit against drug manufacturers in the UK.
+* The benefits of withdrawal include improved cognition, alertness, mobility, reduced risk of incontinence, and a reduced risk of falls and fractures.
+* Benzodiazepines are listed as a potentially inappropriate medication for older adults by the American Geriatrics Society.
+* The elderly are at an increased risk of dependence and are more sensitive to the adverse effects of benzodiazepines.</t>
         </is>
       </c>
     </row>
@@ -3170,6 +8083,79 @@
           <t>Citalopram</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Citalopram</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Citalopram</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Citalopram</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Citalopram</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the articles, here are the key points related to the adverse effects and interactions of bupropion:
+1. **Psychotic Symptoms**: Bupropion has been associated with the induction of psychotic symptoms, particularly at higher than recommended doses. These symptoms can often be alleviated by reducing the dose, ceasing treatment, or adding antipsychotic medication. Concurrent use of antipsychotic medication appears to be protective against these psychotic symptoms.
+2. **Antidepressant Discontinuation Syndrome**: Although there is limited research, some case reports suggest that abrupt discontinuation of bupropion may lead to antidepressant discontinuation syndrome, which can cause withdrawal symptoms such as sensory, gastrointestinal, and psychological symptoms.
+3. **Compulsive Behavior**: Rarely, bupropion has been linked to the induction of compulsive behavior.
+4. **Seizure Risk**: Bupropion, especially the immediate-release formulation, carries a higher risk of seizure compared to many other antidepressants. Caution is advised in patients with a history of seizure disorder.
+5. **Common Adverse Effects**: Common adverse effects of bupropion include dry mouth, nausea, constipation, insomnia, anxiety, tremor, and excessive sweating. Raised blood pressure is also notable.
+6. **Serious Side Effects**: Rare but serious side effects include seizures, liver toxicity, psychosis, and risk of overdose.
+7. **Pregnancy**: Bupropion use during pregnancy may be associated with an increased likelihood of congenital heart defects.
+8. **Mechanism of Action**: Bupropion acts as a norepinephrine-dopamine reuptake inhibitor (NDRI) and a nicotinic receptor antagonist. It is chemically classified as an aminoketone and belongs to the class of substituted cathinones, substituted amphetamines, and substituted phenethylamines.
+9. **Interactions**: Bupropion can interact with other medications and substances, such as psychoactive drugs, alcohol, and sedatives, potentially exacerbating insomnia or other side effects.
+These points highlight the importance of careful monitoring and management when using bupropion, particularly in patients with a history of seizure disorders, those taking other medications, and pregnant women.</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Citalopram</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Citalopram</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Citalopram</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Based on the provided text, here are some key points related to the topics of insomnia, bupropion, and propranolol:
+**Insomnia:**
+* Insomnia can be caused by various conditions, including sleep breathing disorders, use of psychoactive drugs, and withdrawal from substances like alcohol and opioids.
+* Hormonal shifts, life events, and medical conditions can also contribute to insomnia.
+* Poor sleep hygiene, such as consuming caffeine or nicotine, can exacerbate insomnia.
+* Certain neurological disorders, like brain lesions or traumatic brain injury, can also cause insomnia.
+**Bupropion:**
+* Bupropion is an atypical antidepressant used to treat major depressive disorder and seasonal affective disorder.
+* It is a norepinephrine-dopamine reuptake inhibitor (NDRI) and has a unique mechanism of action compared to other antidepressants.
+* Bupropion has several benefits, including not causing sexual dysfunction, weight gain, or sleepiness, and is more effective than SSRIs at improving symptoms of hypersomnia and fatigue.
+* However, bupropion carries a higher risk of seizure than many other antidepressants, and caution is recommended in patients with a history of seizure disorder.
+* Common adverse effects of bupropion include dry mouth, nausea, constipation, insomnia, anxiety, tremor, and excessive sweating.
+* Rare but serious side effects include seizures, liver toxicity, psychosis, and risk of overdose.
+**Propranolol:**
+* Propranolol is a beta blocker used to treat various conditions, including hypertension, angina, and arrhythmias.
+* It is also used to prevent migraines and cluster headaches, and to treat essential tremor.
+* Propranolol may be used to treat severe infantile hemangiomas (IHS) and has shown promise as a superior treatment to corticosteroids.
+* It can also be used to treat acute cardiovascular toxicity caused by sympathomimetics like amphetamine and cocaine.
+* Propranolol is available as propranolol hydrochloride tablets and capsules.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3187,15 +8173,60 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>Primidone</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Primidone</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Primidone</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Primidone</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t>primidone</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>primidone</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>primidone</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Primidone</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Primidone</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Primidone</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
         <is>
           <t>Primidone</t>
         </is>
@@ -3217,15 +8248,60 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>Rifampin</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Rifampin</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>rifabutin</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Rifampin</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Rifampin</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Rifabutin</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>None (insufficient evidence)</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Insufficient evidence</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Rifabutin</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
         <is>
           <t>Rifabutin</t>
         </is>
@@ -3252,12 +8328,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>Sodium zirconium cyclosilicate</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Sodium zirconium cyclosilicate</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Patiromer</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kayexalate</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
           <t>sodium zirconium cyclosilicate</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>sodium zirconium cyclosilicate</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Patiromer</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Hemodialysis</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Sodium zirconium cyclosilicate</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>Sodium Zirconium Cyclosilicate</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Kayexalate</t>
         </is>
       </c>
     </row>
@@ -3282,12 +8403,78 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>Penicillin desensitization</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Penicillin desensitization</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Penicillin desensitization</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
           <t>ceftriaxone</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>ceftriaxone</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ceftriaxone</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>The epidemiology of syphilis is characterized by significant global and regional variations. As of 2012, approximately 0.5% of adults worldwide were infected with syphilis, equating to around 6 million new cases annually. In 1999, it was estimated that 12 million additional people were infected, with the majority of cases occurring in the developing world. Syphilis affects between 700,000 and 1.6 million pregnancies each year, leading to miscarriages, stillbirths, and congenital syphilis. In 2015, syphilis caused about 107,000 deaths, a decrease from 202,000 in 1990. In sub-Saharan Africa, syphilis is responsible for approximately 20% of perinatal deaths.
+In the United States, syphilis rates have been increasing, particularly among men who have sex with men (MSM). As of 2014, about 55,400 new cases were reported annually. African Americans accounted for nearly half of all cases in 2010. By 2020, syphilis rates had more than tripled, with approximately 86% of all cases occurring in men. In 2021, preliminary data from the CDC indicated that 2,677 cases of congenital syphilis were identified in the U.S. population of 332 million.
+Historically, syphilis was very common in Europe during the 18th and 19th centuries. In the early 20th century, the infection rates declined rapidly due to the widespread use of antibiotics. However, since 2000, syphilis rates have been rising in the U.S., Canada, the UK, Australia, and Europe, primarily among MSM. In the U.S., syphilis rates among women have remained stable, while in the UK, they have increased but at a slower rate than among men. In China and Russia, syphilis rates among heterosexuals have increased since the 1990s, attributed to unsafe sexual practices such as sexual promiscuity, prostitution, and decreased use of barrier protection.
+Without treatment, syphilis can have a mortality rate ranging from 8% to 58%, with higher death rates among males. The symptoms of syphilis have become less severe over the 19th and 20th centuries, partly due to the availability of effective treatments and partly due to changes in the bacterium's virulence. Early treatment can prevent complications, and syphilis increases the risk of HIV transmission by two to five times, with coinfection being common in some urban centers.</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Ceftriaxone</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Ceftriaxone</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>Erythromycin</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>The articles provided discuss the causes, epidemiology, and screening of syphilis and chlamydia infections.
+Syphilis:
+* Syphilis is a sexually transmitted infection caused by the bacterium Treponema pallidum subspecies pallidum.
+* It is transmitted primarily by sexual contact or during pregnancy from a mother to her baby.
+* The infection can be spread through intact mucous membranes or compromised skin, and it is highly infectious, with approximately 30-60% of those exposed to primary or secondary syphilis becoming infected.
+* The symptoms of syphilis have become less severe over the 19th and 20th centuries, in part due to widespread availability of effective treatment, and partly due to the virulence of the bacteria.
+* With early treatment, few complications result, but left untreated, it has a mortality rate of 8-58%, with a greater death rate among males.
+Chlamydia:
+* Chlamydia is a sexually transmitted infection caused by the bacterium Chlamydia trachomatis.
+* Most people who are infected have no symptoms, but when symptoms do appear, they may occur only several weeks after infection.
+* Symptoms in women may include vaginal discharge or burning with urination, while symptoms in men may include discharge from the penis, burning with urination, or pain and swelling of one or both testicles.
+* The infection can spread to the upper genital tract in women, causing pelvic inflammatory disease, which may result in future infertility or ectopic pregnancy.
+* Chlamydia can be spread during vaginal, anal, oral, or manual sex and can be passed from an infected mother to her baby during childbirth.
+Screening:
+* For sexually active women who are not pregnant, screening is recommended in those under 25 and others at risk of infection.
+* Risk factors include a history of chlamydial or other sexually transmitted infection, new or multiple sexual partners, and inconsistent condom use.
+* For pregnant women, guidelines vary, but universal screening of pregnant women is recommended by the Centers for Disease Control and Prevention.
+* The US Preventive Services Task Force recommends screening women under 25, while the American Academy of Family Physicians recommends screening women aged 25 or younger.
+In summary, both syphilis and chlamydia are sexually transmitted infections that can have serious consequences if left untreated. Screening is recommended for sexually active women under 25 and others at risk of infection, and universal screening of pregnant women is recommended.</t>
         </is>
       </c>
     </row>
@@ -3312,12 +8499,89 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
           <t>doxycycline</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>doxycycline</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>doxycycline</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the articles, azithromycin is not recommended as a first-line treatment for Lyme disease or syphilis. Here's a summary of the relevant points:
+1. **Lyme Disease:**
+   - For early localized Lyme disease, first-choice antibiotics include doxycycline, amoxicillin, or cefuroxime axetil.
+   - For early disseminated Lyme disease, ceftriaxone or penicillin is recommended.
+   - For late disseminated Lyme disease, ceftriaxone is recommended.
+   - Azithromycin is not mentioned as a first-line treatment for any stage of Lyme disease.
+2. **Syphilis:**
+   - For early-stage syphilis (primary or secondary), the first-line treatment is a single dose of intramuscular benzathine benzylpenicillin.
+   - Doxycycline and tetracycline are alternatives for those allergic to penicillin.
+   - Azithromycin is not recommended as a first-line treatment for early-stage syphilis.
+   - For late-stage syphilis, including neurosyphilis, intravenous penicillin G is recommended.
+   - Ceftriaxone may be used as an alternative if penicillin is contraindicated.
+In summary, azithromycin is not recommended as a first-line treatment for either Lyme disease or syphilis. It is used for a variety of other bacterial infections, but for these specific conditions, other antibiotics are preferred.</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Doxycycline</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>The provided text discusses various medical topics, including Lyme disease, syphilis, chlamydia infection, and azithromycin. Here are the main points from each section:
+**Lyme Disease**
+* Treatment regimens for Lyme disease range from 7-14 days in early localized disease to 14-28 days in late disseminated disease.
+* Neurologic complications of Lyme disease may be treated with doxycycline, although in North America, evidence of efficacy is only indirect.
+* Intravenous antibiotics are preferred for retreatment in case of poor response to oral antibiotics.
+* Antibody levels are not indicative of treatment success, and testing for them is not recommended.
+**Syphilis**
+* The first-line treatment for uncomplicated syphilis is a single dose of intramuscular benzathine benzylpenicillin.
+* Doxycycline and tetracycline are alternative choices for those allergic to penicillin.
+* Ceftriaxone may be used as an alternative to penicillin-based treatment.
+* Treatment at this stage solely limits further progression of the disease and has a limited effect on damage that has already occurred.
+**Chlamydia Infection**
+* Screening is recommended for sexually active women under 25 and others at risk of infection.
+* Guidelines vary for pregnant women, with some recommending universal screening.
+* The effects of screening are uncertain in terms of chlamydia transmission, but screening probably reduces the risk of pelvic inflammatory disease in women.
+**Azithromycin**
+* Azithromycin is an antibiotic medication used to treat several bacterial infections, including middle ear infections, strep throat, pneumonia, traveler's diarrhea, and sexually transmitted infection.
+* Common side effects include nausea, vomiting, diarrhea, and upset stomach.
+* Azithromycin causes QT prolongation, which may cause life-threatening arrhythmias such as torsades de pointes.
+* Its safety during pregnancy and breastfeeding is not confirmed, but it is likely safe.
+Overall, the text provides information on various medical topics, including treatment regimens, side effects, and safety considerations for different medications and infections.</t>
         </is>
       </c>
     </row>
@@ -3350,6 +8614,79 @@
           <t>Regadenoson</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Based on the information provided, it is clear that asthma and chronic obstructive pulmonary disease (COPD) are respiratory conditions that require careful management, particularly when considering the use of medications like beta-blockers and bronchodilators. Here are some key points and considerations:
+### Asthma
+- **Beta-blocker Use**: Non-selective beta-blockers are generally contraindicated in asthma patients due to their potential to exacerbate airway constriction. Cardioselective beta-blockers may be used cautiously in patients with mild to moderate asthma, but they should be used at the lowest effective dose.
+- **Bronchodilators**: Short-acting beta2-adrenergic agonists (SABA) are used on an as-needed basis to relieve acute symptoms. Long-acting beta2-adrenergic agonists (LABA) are used for maintenance therapy.
+- **Testing**: Bronchial provocation testing can help diagnose asthma, but it is not specific and can also be positive in other conditions like allergic rhinitis, cystic fibrosis, and COPD.
+### Chronic Obstructive Pulmonary Disease (COPD)
+- **Bronchodilators**: Inhaled short-acting bronchodilators are used for acute symptoms, while long-acting bronchodilators are used for maintenance therapy. Combination therapy with LABA and long-acting muscarinic antagonists (LAMA) is often recommended for more severe symptoms.
+- **Assessment**: Spirometry is used to determine the severity of airflow limitation. The Global Initiative for Chronic Obstructive Lung Disease (GOLD) guidelines classify patients based on symptom burden and exacerbation history.
+- **Pharmacological Treatment**: Dual bronchodilator therapy (LABA + LAMA) is recommended for more severe symptoms, and inhaled corticosteroids may be added for patients with frequent exacerbations.
+### Coronary Artery Disease (CAD)
+- **Stable Angina**: Stable angina is managed with medications like nitroglycerine, which works by releasing nitric oxide (NO) to cause vasodilation and improve blood flow to the heart.
+- **Stress Testing**: Various forms of cardiac stress tests (ECG, echocardiography, scintigraphy) may be used to detect changes in blood flow and identify stenosis of the coronary arteries.
+- **Management**: Nitroglycerine is used to alleviate acute symptoms and prevent the onset of angina during exertion. In severe cases, angioplasty or bypass surgery may be necessary.
+### Contraindications
+- **Beta-blockers**: Contraindicated in patients with asthma, severe bradycardia, cardiogenic shock, and severe hypotension. Caution is advised in patients with hyperthyroidism, bradycardia, and certain arrhythmias.
+- **Labetalol**: Contraindicated in patients with overt cardiac failure, greater-than-first-degree heart block, severe bradycardia, cardiogenic shock, severe hypotension, and obstructive airway disease including asthma.
+### Summary
+- **Asthma**: Avoid non-selective beta-blockers; use cardioselective beta-blockers cautiously. Use SABA for acute symptoms and LABA for maintenance.
+- **COPD**: Use short-acting bronchodilators for acute symptoms and LABA or LAMA for maintenance. Dual bronchodilator therapy is recommended for severe symptoms.
+- **CAD**: Use nitroglycerine for acute angina and manage stable angina with stress testing and appropriate interventions.
+These guidelines and considerations are crucial for the effective management of respiratory and cardiovascular conditions, ensuring patient safety and optimal treatment outcomes.</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Regadenoson</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>The provided text discusses various medical conditions and treatments, including asthma, chronic obstructive pulmonary disease (COPD), coronary artery disease, and beta blockers. Here are some key points:
+1. **Asthma**: The 2007 National Heart, Lung, and Blood Institute (NHLBI) asthma guidelines recommend against the use of non-selective beta blockers in asthmatics, while allowing for the use of cardio-selective beta blockers. Beta blockers can exacerbate asthma and worsen symptoms.
+2. **COPD**: Inhaled short-acting bronchodilators are the primary medications used on an as-needed basis for COPD. Long-acting bronchodilators, such as LABAs and LAMAs, are used for maintenance therapy. The GOLD 2022 report recommends pharmacological treatment with a LABA or LAMA as initial monotherapy for most patients.
+3. **Coronary Artery Disease (CAD)**: Stable angina is the most common manifestation of ischemic heart disease and is associated with reduced quality of life and increased mortality. Nitroglycerine may be used to alleviate acute symptoms of stable angina or to prevent the onset of angina.
+4. **Beta Blockers**: Beta blockers are contraindicated in people with overt cardiac failure, greater-than-first-degree heart block, severe bradycardia, cardiogenic shock, severe hypotension, or a history of obstructive airway disease, including asthma.
+5. **Assessment of COPD**: Several methods can be used to assess the effects and severity of COPD, including screening questionnaires, spirometry, and the GOLD classification system.
+6. **Coronary Artery Disease**: Stable angina is caused by epicardial coronary stenosis, which results in reduced blood flow and oxygen supply to the myocardium. Various forms of cardiac stress tests may be used to induce symptoms and detect changes.
+7. **Nitroglycerine**: Nitroglycerine is used to alleviate acute symptoms of stable angina or to prevent the onset of angina. It works by forming free radical nitric oxide, which activates guanylate cyclase and stimulates the release of cyclic GMP, leading to smooth muscle relaxation and vasodilation.
+These points highlight the importance of careful consideration and individualization of treatment for patients with various medical conditions, including asthma, COPD, and coronary artery disease.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3372,12 +8709,103 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>Low molecular weight heparin</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>LMWH</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Low molecular weight heparin</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>LMWH</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>LMWH</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>LMWH</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Based on the information provided in the articles, here are the key points regarding risk factors for VTE (Venous Thromboembolism) and pulmonary embolism, as well as the medical uses and adverse effects of warfarin:
+### Risk Factors for VTE and Pulmonary Embolism
+1. **Demographics and Ethnicity**:
+   - VTE is more common in individuals aged 70 years or older, with a 18% higher incidence in males compared to females.
+   - Asian, Asian-American, Native American, and Hispanic individuals have a lower VTE risk compared to White or Black people.
+   - Populations in Asia have VTE rates at 15 to 20% of what is seen in Western countries, with an increasing incidence over time.
+2. **Medical Conditions and Situations**:
+   - VTE occurs in association with hospitalization or nursing home residence about 60% of the time.
+   - Active cancer is associated with VTE in about 20% of cases.
+   - Central venous catheters or transvenous pacemakers are linked to VTE in about 9% of cases.
+   - During pregnancy and postpartum, acute VTE occurs in about 1.2 per 1,000 deliveries.
+   - After surgery, VTE develops in about 10 per 1,000 people after total or partial knee replacement, and in about 5 per 1,000 after total or partial hip replacement.
+3. **Genetic and Environmental Factors**:
+   - About 4-8% of North American and European populations have thrombophilia, commonly factor V Leiden and prothrombin G20210A mutations.
+   - Non-O blood type is present in about 50% of the general population and 70% of those with VTE.
+   - Immobilization, injury, obesity, and cancer are risk factors due to alterations in blood flow and procoagulant states.
+   - Genetic thrombophilia (e.g., factor V Leiden, prothrombin mutation G20210A, protein C deficiency, protein S deficiency, antithrombin deficiency, hyperhomocysteinemia, and plasminogen/fibrinolysis disorders) and acquired thrombophilia (e.g., antiphospholipid syndrome, nephrotic syndrome, paroxysmal nocturnal hemoglobinuria) increase the risk of VTE.
+4. **Specific Conditions**:
+   - Pancreatic and colon cancer patients are at higher risk due to the release of procoagulants.
+   - Pregnancy and childbirth put women at risk due to a hypercoagulable state.
+   - Use of estrogen-containing medications (e.g., oral contraceptives, menopausal hormone therapy, transgender hormone therapy) increases the risk.
+### Medical Uses of Warfarin
+1. **Dosing and Monitoring**:
+   - Warfarin dosing is complex due to interactions with medications and foods.
+   - Regular monitoring of INR (International Normalized Ratio) is essential to maintain therapeutic levels.
+   - Point-of-care testing (finger prick) is increasingly used for convenience and accuracy.
+2. **Alternative Anticoagulants**:
+   - Other coumarins like acenocoumarol and phenprocoumon are used in some countries.
+   - Newer anticoagulants such as dabigatran, apixaban, edoxaban, and rivaroxaban offer efficacy without the need for monitoring.
+   - Reversal agents are available for dabigatran (idarucizumab) and apixaban, rivaroxaban (andexanet alfa).
+### Adverse Effects of Warfarin
+1. **Bleeding**:
+   - The most common side effect is hemorrhage, with a typical yearly rate of 1-3%.
+   - Severe bleeding risks include intracerebral hemorrhage and hemorrhagic stroke.
+   - Risk increases with INR levels exceeding 4.5.
+   - Risk scores like HAS-BLED and ATRIA are used to predict bleeding risk.
+2. **Warfarin Necrosis**:
+   - A rare but serious complication, more frequent in patients with protein C deficiency.
+   - Occurs due to the initial decrease in protein C levels faster than coagulation factors, leading to massive thrombosis and skin necrosis.
+These points summarize the key aspects of VTE risk factors and the medical uses and adverse effects of warfarin, providing a comprehensive overview of the topic.</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Low molecular weight heparin (LMWH)</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Low molecular weight heparin (LMWH)</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>LMWH</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>The provided text discusses various aspects of venous thromboembolism (VTE), including its incidence, risk factors, and treatment. Some key points from the text are:
+* VTE is a significant cause of morbidity and mortality, with approximately 400,000 Americans developing an initial VTE each year.
+* The risk of VTE is higher in individuals with certain conditions, such as cancer, pregnancy, and estrogen-containing medication use.
+* The development of VTE is often due to a combination of factors, including alterations in blood flow, factors in the vessel wall, and factors affecting the properties of the blood (Virchow's triad).
+* Warfarin is a commonly used anticoagulant for the treatment and prevention of VTE, but it has several potential side effects, including bleeding.
+* The dosing of warfarin requires close monitoring of the degree of anticoagulation, typically through regular blood tests measuring the international normalized ratio (INR).
+* Alternative anticoagulants, such as dabigatran, apixaban, edoxaban, and rivaroxaban, are available for use in some countries, and reversal agents are available for dabigatran and apixaban.
+Overall, the text highlights the importance of understanding the risk factors and treatment options for VTE, as well as the potential side effects of anticoagulant therapy.</t>
         </is>
       </c>
     </row>
@@ -3402,10 +8830,55 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>Dietary restriction of tyrosine and phenylalanine</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Dietary restriction of tyrosine and phenylalanine</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Dietary restriction of tyrosine and phenylalanine</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>dietary restriction of tyrosine and phenylalanine</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>dietary restriction of tyrosine and phenylalanine</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>dietary restriction of tyrosine and phenylalanine</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>dietary restriction of tyrosine and phenylalanine</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Tyrosine restriction</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Tyrosine restriction</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Low-protein diet</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
         <is>
           <t>Low-protein diet</t>
         </is>
@@ -3432,10 +8905,55 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>MRCP</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>MRCP</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>MRCP</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>MRI</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
         <is>
           <t>MRI</t>
         </is>
@@ -3452,7 +8970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3484,45 +9002,189 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.62</v>
+        <v>0.41</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6836666666666666</v>
+        <v>0.4746666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>qwen2.5</t>
+          <t>hu</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6033333333333334</v>
+        <v>0.6201696428571429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>llama3.1</t>
+          <t>hu</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5</v>
       </c>
       <c r="C4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6836666666666666</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hu</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.719857142857143</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>qwen2.5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4966666666666666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>qwen2.5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6156666666666667</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>qwen2.5</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6033333333333334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>qwen2.5</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3654905131295873</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>llama3.1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>llama3.1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.613</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>llama3.1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.52</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D12" t="n">
         <v>0.5875714285714285</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>llama3.1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3367605917081991</v>
       </c>
     </row>
   </sheetData>
